--- a/data/2021-2025_推薦v2.xlsx
+++ b/data/2021-2025_推薦v2.xlsx
@@ -8570,10 +8570,10 @@
         <v>24.6</v>
       </c>
       <c r="G2">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="H2">
-        <v>20.73</v>
+        <v>19.11</v>
       </c>
       <c r="I2" t="s">
         <v>1244</v>
@@ -8672,10 +8672,10 @@
         <v>14.05</v>
       </c>
       <c r="G5">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H5">
-        <v>13.52</v>
+        <v>9.25</v>
       </c>
       <c r="I5" t="s">
         <v>1244</v>
@@ -8707,10 +8707,10 @@
         <v>38.6</v>
       </c>
       <c r="G6">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H6">
-        <v>4.15</v>
+        <v>3.11</v>
       </c>
       <c r="I6" t="s">
         <v>1244</v>
@@ -8748,7 +8748,7 @@
         <v>0.57</v>
       </c>
       <c r="I7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J7" t="s">
         <v>1249</v>
@@ -8847,10 +8847,10 @@
         <v>19.15</v>
       </c>
       <c r="G10">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="H10">
-        <v>13.05</v>
+        <v>10.97</v>
       </c>
       <c r="I10" t="s">
         <v>1244</v>
@@ -8888,7 +8888,7 @@
         <v>1.18</v>
       </c>
       <c r="I11" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J11" t="s">
         <v>1249</v>
@@ -8923,7 +8923,7 @@
         <v>2.8</v>
       </c>
       <c r="I12" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J12" t="s">
         <v>1249</v>
@@ -8958,7 +8958,7 @@
         <v>1.84</v>
       </c>
       <c r="I13" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J13" t="s">
         <v>1249</v>
@@ -9028,7 +9028,7 @@
         <v>1.07</v>
       </c>
       <c r="I15" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J15" t="s">
         <v>1249</v>
@@ -9063,7 +9063,7 @@
         <v>4.18</v>
       </c>
       <c r="I16" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J16" t="s">
         <v>1249</v>
@@ -9095,10 +9095,10 @@
         <v>810</v>
       </c>
       <c r="H17">
-        <v>66.98999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="I17" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J17" t="s">
         <v>1250</v>
@@ -9127,10 +9127,10 @@
         <v>13.65</v>
       </c>
       <c r="G18">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="H18">
-        <v>26.37</v>
+        <v>20.51</v>
       </c>
       <c r="I18" t="s">
         <v>1244</v>
@@ -9162,13 +9162,13 @@
         <v>8.74</v>
       </c>
       <c r="G19">
-        <v>620</v>
+        <v>540</v>
       </c>
       <c r="H19">
-        <v>49.66</v>
+        <v>61.78</v>
       </c>
       <c r="I19" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J19" t="s">
         <v>1251</v>
@@ -9197,10 +9197,10 @@
         <v>12.8</v>
       </c>
       <c r="G20">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="H20">
-        <v>21.56</v>
+        <v>19.69</v>
       </c>
       <c r="I20" t="s">
         <v>1244</v>
@@ -9302,10 +9302,10 @@
         <v>5.83</v>
       </c>
       <c r="G23">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H23">
-        <v>22.3</v>
+        <v>18.87</v>
       </c>
       <c r="I23" t="s">
         <v>1244</v>
@@ -9375,10 +9375,10 @@
         <v>250</v>
       </c>
       <c r="H25">
-        <v>23.65</v>
+        <v>33.78</v>
       </c>
       <c r="I25" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J25" t="s">
         <v>1252</v>
@@ -9413,7 +9413,7 @@
         <v>0.97</v>
       </c>
       <c r="I26" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J26" t="s">
         <v>1249</v>
@@ -9477,10 +9477,10 @@
         <v>11.7</v>
       </c>
       <c r="G28">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H28">
-        <v>25.64</v>
+        <v>17.09</v>
       </c>
       <c r="I28" t="s">
         <v>1244</v>
@@ -9544,13 +9544,13 @@
         <v>18.5</v>
       </c>
       <c r="G30">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H30">
-        <v>4.92</v>
+        <v>5.95</v>
       </c>
       <c r="I30" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J30" t="s">
         <v>1252</v>
@@ -9579,13 +9579,13 @@
         <v>39.9</v>
       </c>
       <c r="G31">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="H31">
-        <v>2.95</v>
+        <v>3.41</v>
       </c>
       <c r="I31" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J31" t="s">
         <v>1253</v>
@@ -9684,10 +9684,10 @@
         <v>40</v>
       </c>
       <c r="H34">
-        <v>0.89</v>
+        <v>1.27</v>
       </c>
       <c r="I34" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J34" t="s">
         <v>1251</v>
@@ -9722,7 +9722,7 @@
         <v>0.4</v>
       </c>
       <c r="I35" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K35" t="s">
         <v>1291</v>
@@ -9783,10 +9783,10 @@
         <v>11.1</v>
       </c>
       <c r="G37">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H37">
-        <v>17.12</v>
+        <v>11.71</v>
       </c>
       <c r="I37" t="s">
         <v>1244</v>
@@ -9824,7 +9824,7 @@
         <v>2.23</v>
       </c>
       <c r="I38" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J38" t="s">
         <v>1249</v>
@@ -9859,7 +9859,7 @@
         <v>0.93</v>
       </c>
       <c r="I39" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K39" t="s">
         <v>1260</v>
@@ -9920,10 +9920,10 @@
         <v>175</v>
       </c>
       <c r="H41">
-        <v>9.42</v>
+        <v>13.46</v>
       </c>
       <c r="I41" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J41" t="s">
         <v>1252</v>
@@ -9990,7 +9990,7 @@
         <v>1.89</v>
       </c>
       <c r="I43" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J43" t="s">
         <v>1249</v>
@@ -10019,13 +10019,13 @@
         <v>11.45</v>
       </c>
       <c r="G44">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H44">
-        <v>0.87</v>
+        <v>0.52</v>
       </c>
       <c r="I44" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K44" t="s">
         <v>1299</v>
@@ -10051,13 +10051,13 @@
         <v>7.84</v>
       </c>
       <c r="G45">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H45">
-        <v>17.86</v>
+        <v>23.47</v>
       </c>
       <c r="I45" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J45" t="s">
         <v>1251</v>
@@ -10086,13 +10086,13 @@
         <v>158</v>
       </c>
       <c r="G46">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="H46">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="I46" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J46" t="s">
         <v>1249</v>
@@ -10121,13 +10121,13 @@
         <v>115.5</v>
       </c>
       <c r="G47">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H47">
-        <v>1.13</v>
+        <v>0.95</v>
       </c>
       <c r="I47" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J47" t="s">
         <v>1249</v>
@@ -10162,7 +10162,7 @@
         <v>5.3</v>
       </c>
       <c r="I48" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J48" t="s">
         <v>1249</v>
@@ -10191,10 +10191,10 @@
         <v>11.2</v>
       </c>
       <c r="G49">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H49">
-        <v>14.29</v>
+        <v>10.71</v>
       </c>
       <c r="I49" t="s">
         <v>1244</v>
@@ -10229,7 +10229,7 @@
         <v>0.4</v>
       </c>
       <c r="I50" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K50" t="s">
         <v>1305</v>
@@ -10290,10 +10290,10 @@
         <v>17.4</v>
       </c>
       <c r="G52">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="H52">
-        <v>14.37</v>
+        <v>12.07</v>
       </c>
       <c r="I52" t="s">
         <v>1244</v>
@@ -10366,7 +10366,7 @@
         <v>7.14</v>
       </c>
       <c r="I54" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J54" t="s">
         <v>1249</v>
@@ -10401,7 +10401,7 @@
         <v>1.71</v>
       </c>
       <c r="I55" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J55" t="s">
         <v>1249</v>
@@ -10436,7 +10436,7 @@
         <v>0.91</v>
       </c>
       <c r="I56" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K56" t="s">
         <v>1311</v>
@@ -10462,10 +10462,10 @@
         <v>22.6</v>
       </c>
       <c r="G57">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H57">
-        <v>9.73</v>
+        <v>6.19</v>
       </c>
       <c r="I57" t="s">
         <v>1244</v>
@@ -10497,10 +10497,10 @@
         <v>94</v>
       </c>
       <c r="G58">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H58">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="I58" t="s">
         <v>1246</v>
@@ -10538,7 +10538,7 @@
         <v>2.21</v>
       </c>
       <c r="I59" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J59" t="s">
         <v>1249</v>
@@ -10605,10 +10605,10 @@
         <v>35</v>
       </c>
       <c r="H61">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I61" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="J61" t="s">
         <v>1252</v>
@@ -10640,10 +10640,10 @@
         <v>270</v>
       </c>
       <c r="H62">
-        <v>6.1</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I62" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J62" t="s">
         <v>1252</v>
@@ -10672,13 +10672,13 @@
         <v>131.5</v>
       </c>
       <c r="G63">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H63">
-        <v>0.99</v>
+        <v>0.84</v>
       </c>
       <c r="I63" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J63" t="s">
         <v>1249</v>
@@ -10748,7 +10748,7 @@
         <v>1.59</v>
       </c>
       <c r="I65" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J65" t="s">
         <v>1249</v>
@@ -10783,7 +10783,7 @@
         <v>11.28</v>
       </c>
       <c r="I66" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J66" t="s">
         <v>1249</v>
@@ -10818,7 +10818,7 @@
         <v>3.6</v>
       </c>
       <c r="I67" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J67" t="s">
         <v>1249</v>
@@ -10847,10 +10847,10 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="H68">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I68" t="s">
         <v>1244</v>
@@ -10882,10 +10882,10 @@
         <v>32.05</v>
       </c>
       <c r="G69">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="H69">
-        <v>11.98</v>
+        <v>8.99</v>
       </c>
       <c r="I69" t="s">
         <v>1244</v>
@@ -10987,13 +10987,13 @@
         <v>35.6</v>
       </c>
       <c r="G72">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H72">
-        <v>1.12</v>
+        <v>0.67</v>
       </c>
       <c r="I72" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K72" t="s">
         <v>1325</v>
@@ -11054,10 +11054,10 @@
         <v>39.3</v>
       </c>
       <c r="G74">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H74">
-        <v>4.07</v>
+        <v>3.05</v>
       </c>
       <c r="I74" t="s">
         <v>1244</v>
@@ -11089,13 +11089,13 @@
         <v>17.1</v>
       </c>
       <c r="G75">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H75">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="I75" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J75" t="s">
         <v>1252</v>
@@ -11124,13 +11124,13 @@
         <v>32.3</v>
       </c>
       <c r="G76">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="H76">
-        <v>4.98</v>
+        <v>5.26</v>
       </c>
       <c r="I76" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J76" t="s">
         <v>1252</v>
@@ -11159,10 +11159,10 @@
         <v>46.15</v>
       </c>
       <c r="G77">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H77">
-        <v>2.82</v>
+        <v>2.38</v>
       </c>
       <c r="I77" t="s">
         <v>1244</v>
@@ -11194,13 +11194,13 @@
         <v>46.9</v>
       </c>
       <c r="G78">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H78">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="I78" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="K78" t="s">
         <v>1331</v>
@@ -11229,10 +11229,10 @@
         <v>200</v>
       </c>
       <c r="H79">
-        <v>12.13</v>
+        <v>17.33</v>
       </c>
       <c r="I79" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J79" t="s">
         <v>1252</v>
@@ -11299,10 +11299,10 @@
         <v>250</v>
       </c>
       <c r="H81">
-        <v>9.23</v>
+        <v>13.19</v>
       </c>
       <c r="I81" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J81" t="s">
         <v>1252</v>
@@ -11372,7 +11372,7 @@
         <v>0.63</v>
       </c>
       <c r="I83" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J83" t="s">
         <v>1249</v>
@@ -11401,13 +11401,13 @@
         <v>26.35</v>
       </c>
       <c r="G84">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H84">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="I84" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="K84" t="s">
         <v>1337</v>
@@ -11433,10 +11433,10 @@
         <v>29.1</v>
       </c>
       <c r="G85">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="H85">
-        <v>8.93</v>
+        <v>8.25</v>
       </c>
       <c r="I85" t="s">
         <v>1244</v>
@@ -11503,10 +11503,10 @@
         <v>31.6</v>
       </c>
       <c r="G87">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="H87">
-        <v>9.109999999999999</v>
+        <v>6.08</v>
       </c>
       <c r="I87" t="s">
         <v>1244</v>
@@ -11538,13 +11538,13 @@
         <v>59.6</v>
       </c>
       <c r="G88">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="H88">
-        <v>3.52</v>
+        <v>3.83</v>
       </c>
       <c r="I88" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J88" t="s">
         <v>1252</v>
@@ -11608,13 +11608,13 @@
         <v>12.35</v>
       </c>
       <c r="G90">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H90">
-        <v>7.13</v>
+        <v>5.83</v>
       </c>
       <c r="I90" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J90" t="s">
         <v>1249</v>
@@ -11754,7 +11754,7 @@
         <v>1.98</v>
       </c>
       <c r="I94" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J94" t="s">
         <v>1249</v>
@@ -11783,13 +11783,13 @@
         <v>26</v>
       </c>
       <c r="G95">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H95">
-        <v>1.54</v>
+        <v>0.92</v>
       </c>
       <c r="I95" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J95" t="s">
         <v>1249</v>
@@ -11818,10 +11818,10 @@
         <v>107.5</v>
       </c>
       <c r="G96">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="H96">
-        <v>3.72</v>
+        <v>2.98</v>
       </c>
       <c r="I96" t="s">
         <v>1244</v>
@@ -11853,10 +11853,10 @@
         <v>17.3</v>
       </c>
       <c r="G97">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H97">
-        <v>8.67</v>
+        <v>2.89</v>
       </c>
       <c r="I97" t="s">
         <v>1244</v>
@@ -11891,10 +11891,10 @@
         <v>130</v>
       </c>
       <c r="H98">
-        <v>1.52</v>
+        <v>2.18</v>
       </c>
       <c r="I98" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J98" t="s">
         <v>1251</v>
@@ -11958,10 +11958,10 @@
         <v>19.1</v>
       </c>
       <c r="G100">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="H100">
-        <v>20.42</v>
+        <v>18.32</v>
       </c>
       <c r="I100" t="s">
         <v>1244</v>
@@ -11993,10 +11993,10 @@
         <v>77.7</v>
       </c>
       <c r="G101">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H101">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="I101" t="s">
         <v>1245</v>
@@ -12031,7 +12031,7 @@
         <v>4.25</v>
       </c>
       <c r="I102" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J102" t="s">
         <v>1249</v>
@@ -12092,10 +12092,10 @@
         <v>17.35</v>
       </c>
       <c r="G104">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="H104">
-        <v>24.78</v>
+        <v>23.63</v>
       </c>
       <c r="I104" t="s">
         <v>1244</v>
@@ -12133,7 +12133,7 @@
         <v>1.68</v>
       </c>
       <c r="I105" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J105" t="s">
         <v>1249</v>
@@ -12162,13 +12162,13 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G106">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="H106">
-        <v>15.03</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I106" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J106" t="s">
         <v>1249</v>
@@ -12197,13 +12197,13 @@
         <v>14.55</v>
       </c>
       <c r="G107">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="H107">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="I107" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J107" t="s">
         <v>1249</v>
@@ -12267,10 +12267,10 @@
         <v>10.6</v>
       </c>
       <c r="G109">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="H109">
-        <v>32.26</v>
+        <v>20.94</v>
       </c>
       <c r="I109" t="s">
         <v>1244</v>
@@ -12302,10 +12302,10 @@
         <v>15.35</v>
       </c>
       <c r="G110">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H110">
-        <v>9.119999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="I110" t="s">
         <v>1244</v>
@@ -12337,10 +12337,10 @@
         <v>39.15</v>
       </c>
       <c r="G111">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H111">
-        <v>4.85</v>
+        <v>3.32</v>
       </c>
       <c r="I111" t="s">
         <v>1244</v>
@@ -12372,13 +12372,13 @@
         <v>28.2</v>
       </c>
       <c r="G112">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H112">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="I112" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J112" t="s">
         <v>1253</v>
@@ -12413,7 +12413,7 @@
         <v>2.91</v>
       </c>
       <c r="I113" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J113" t="s">
         <v>1249</v>
@@ -12483,7 +12483,7 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J115" t="s">
         <v>1249</v>
@@ -12512,10 +12512,10 @@
         <v>12.4</v>
       </c>
       <c r="G116">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="H116">
-        <v>22.58</v>
+        <v>20.97</v>
       </c>
       <c r="I116" t="s">
         <v>1244</v>
@@ -12585,10 +12585,10 @@
         <v>40</v>
       </c>
       <c r="H118">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="I118" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J118" t="s">
         <v>1251</v>
@@ -12617,13 +12617,13 @@
         <v>15.1</v>
       </c>
       <c r="G119">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H119">
-        <v>5.96</v>
+        <v>5.17</v>
       </c>
       <c r="I119" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J119" t="s">
         <v>1249</v>
@@ -12652,13 +12652,13 @@
         <v>58</v>
       </c>
       <c r="G120">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H120">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="I120" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J120" t="s">
         <v>1249</v>
@@ -12687,13 +12687,13 @@
         <v>21.5</v>
       </c>
       <c r="G121">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H121">
-        <v>8.140000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="I121" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J121" t="s">
         <v>1252</v>
@@ -12760,7 +12760,7 @@
         <v>0.85</v>
       </c>
       <c r="I123" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J123" t="s">
         <v>1249</v>
@@ -12824,13 +12824,13 @@
         <v>59.5</v>
       </c>
       <c r="G125">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H125">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="I125" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J125" t="s">
         <v>1252</v>
@@ -12894,13 +12894,13 @@
         <v>211.5</v>
       </c>
       <c r="G127">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H127">
-        <v>0.9</v>
+        <v>0.61</v>
       </c>
       <c r="I127" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J127" t="s">
         <v>1249</v>
@@ -12929,13 +12929,13 @@
         <v>16.75</v>
       </c>
       <c r="G128">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="H128">
-        <v>10.53</v>
+        <v>10.75</v>
       </c>
       <c r="I128" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J128" t="s">
         <v>1253</v>
@@ -12964,13 +12964,13 @@
         <v>91.40000000000001</v>
       </c>
       <c r="G129">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H129">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="I129" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J129" t="s">
         <v>1252</v>
@@ -13031,10 +13031,10 @@
         <v>10.5</v>
       </c>
       <c r="G131">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H131">
-        <v>23.81</v>
+        <v>14.29</v>
       </c>
       <c r="I131" t="s">
         <v>1244</v>
@@ -13066,10 +13066,10 @@
         <v>258</v>
       </c>
       <c r="G132">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H132">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="I132" t="s">
         <v>1245</v>
@@ -13136,10 +13136,10 @@
         <v>52.6</v>
       </c>
       <c r="G134">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="H134">
-        <v>5.51</v>
+        <v>5.13</v>
       </c>
       <c r="I134" t="s">
         <v>1244</v>
@@ -13241,10 +13241,10 @@
         <v>450</v>
       </c>
       <c r="H137">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="I137" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J137" t="s">
         <v>1252</v>
@@ -13273,10 +13273,10 @@
         <v>50</v>
       </c>
       <c r="G138">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="H138">
-        <v>6.12</v>
+        <v>4.2</v>
       </c>
       <c r="I138" t="s">
         <v>1244</v>
@@ -13343,10 +13343,10 @@
         <v>30.75</v>
       </c>
       <c r="G140">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H140">
-        <v>8.130000000000001</v>
+        <v>4.88</v>
       </c>
       <c r="I140" t="s">
         <v>1244</v>
@@ -13378,13 +13378,13 @@
         <v>109</v>
       </c>
       <c r="G141">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H141">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="I141" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J141" t="s">
         <v>1252</v>
@@ -13483,10 +13483,10 @@
         <v>24.15</v>
       </c>
       <c r="G144">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="H144">
-        <v>11.59</v>
+        <v>10.26</v>
       </c>
       <c r="I144" t="s">
         <v>1244</v>
@@ -13553,13 +13553,13 @@
         <v>42.3</v>
       </c>
       <c r="G146">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H146">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="I146" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J146" t="s">
         <v>1249</v>
@@ -13588,13 +13588,13 @@
         <v>116</v>
       </c>
       <c r="G147">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H147">
-        <v>0.97</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I147" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J147" t="s">
         <v>1249</v>
@@ -13623,13 +13623,13 @@
         <v>50.6</v>
       </c>
       <c r="G148">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="H148">
-        <v>2.21</v>
+        <v>2.77</v>
       </c>
       <c r="I148" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J148" t="s">
         <v>1250</v>
@@ -13664,7 +13664,7 @@
         <v>2.54</v>
       </c>
       <c r="I149" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J149" t="s">
         <v>1249</v>
@@ -13693,10 +13693,10 @@
         <v>34.8</v>
       </c>
       <c r="G150">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="H150">
-        <v>21.55</v>
+        <v>20.4</v>
       </c>
       <c r="I150" t="s">
         <v>1244</v>
@@ -13833,13 +13833,13 @@
         <v>70.59999999999999</v>
       </c>
       <c r="G154">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H154">
-        <v>3.12</v>
+        <v>1.98</v>
       </c>
       <c r="I154" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J154" t="s">
         <v>1249</v>
@@ -13868,13 +13868,13 @@
         <v>80.5</v>
       </c>
       <c r="G155">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H155">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="I155" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J155" t="s">
         <v>1249</v>
@@ -13906,7 +13906,7 @@
         <v>150</v>
       </c>
       <c r="H156">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="I156" t="s">
         <v>1245</v>
@@ -13944,7 +13944,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I157" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J157" t="s">
         <v>1249</v>
@@ -14014,7 +14014,7 @@
         <v>12.77</v>
       </c>
       <c r="I159" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J159" t="s">
         <v>1249</v>
@@ -14046,7 +14046,7 @@
         <v>70</v>
       </c>
       <c r="H160">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="I160" t="s">
         <v>1245</v>
@@ -14078,13 +14078,13 @@
         <v>26.25</v>
       </c>
       <c r="G161">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="H161">
-        <v>3.63</v>
+        <v>3.96</v>
       </c>
       <c r="I161" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J161" t="s">
         <v>1252</v>
@@ -14148,10 +14148,10 @@
         <v>51.3</v>
       </c>
       <c r="G163">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H163">
-        <v>3.12</v>
+        <v>2.34</v>
       </c>
       <c r="I163" t="s">
         <v>1244</v>
@@ -14218,10 +14218,10 @@
         <v>14.75</v>
       </c>
       <c r="G165">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="H165">
-        <v>12.2</v>
+        <v>10.85</v>
       </c>
       <c r="I165" t="s">
         <v>1244</v>
@@ -14288,10 +14288,10 @@
         <v>16.55</v>
       </c>
       <c r="G167">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H167">
-        <v>21.15</v>
+        <v>15.11</v>
       </c>
       <c r="I167" t="s">
         <v>1244</v>
@@ -14323,10 +14323,10 @@
         <v>34.8</v>
       </c>
       <c r="G168">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="H168">
-        <v>6.61</v>
+        <v>5.46</v>
       </c>
       <c r="I168" t="s">
         <v>1244</v>
@@ -14358,13 +14358,13 @@
         <v>50.9</v>
       </c>
       <c r="G169">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="H169">
-        <v>3.14</v>
+        <v>2.2</v>
       </c>
       <c r="I169" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J169" t="s">
         <v>1249</v>
@@ -14396,7 +14396,7 @@
         <v>80</v>
       </c>
       <c r="H170">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="I170" t="s">
         <v>1245</v>
@@ -14434,7 +14434,7 @@
         <v>0.91</v>
       </c>
       <c r="I171" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J171" t="s">
         <v>1249</v>
@@ -14539,7 +14539,7 @@
         <v>8.789999999999999</v>
       </c>
       <c r="I174" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J174" t="s">
         <v>1249</v>
@@ -14603,10 +14603,10 @@
         <v>60.8</v>
       </c>
       <c r="G176">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H176">
-        <v>3.12</v>
+        <v>2.14</v>
       </c>
       <c r="I176" t="s">
         <v>1244</v>
@@ -14638,13 +14638,13 @@
         <v>20.6</v>
       </c>
       <c r="G177">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H177">
-        <v>1.36</v>
+        <v>0.97</v>
       </c>
       <c r="I177" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J177" t="s">
         <v>1249</v>
@@ -14673,10 +14673,10 @@
         <v>84.7</v>
       </c>
       <c r="G178">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="H178">
-        <v>8.85</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="I178" t="s">
         <v>1244</v>
@@ -14708,13 +14708,13 @@
         <v>19.7</v>
       </c>
       <c r="G179">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H179">
-        <v>8.119999999999999</v>
+        <v>4.87</v>
       </c>
       <c r="I179" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J179" t="s">
         <v>1249</v>
@@ -14743,13 +14743,13 @@
         <v>13.2</v>
       </c>
       <c r="G180">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H180">
-        <v>6.67</v>
+        <v>5.45</v>
       </c>
       <c r="I180" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J180" t="s">
         <v>1249</v>
@@ -14781,7 +14781,7 @@
         <v>100</v>
       </c>
       <c r="H181">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="I181" t="s">
         <v>1245</v>
@@ -14918,7 +14918,7 @@
         <v>140</v>
       </c>
       <c r="H185">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
       <c r="I185" t="s">
         <v>1246</v>
@@ -14982,10 +14982,10 @@
         <v>15.45</v>
       </c>
       <c r="G187">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="H187">
-        <v>34.95</v>
+        <v>32.36</v>
       </c>
       <c r="I187" t="s">
         <v>1244</v>
@@ -15052,10 +15052,10 @@
         <v>54.8</v>
       </c>
       <c r="G189">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H189">
-        <v>8.94</v>
+        <v>6.39</v>
       </c>
       <c r="I189" t="s">
         <v>1244</v>
@@ -15122,10 +15122,10 @@
         <v>52.3</v>
       </c>
       <c r="G191">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H191">
-        <v>4.21</v>
+        <v>2.68</v>
       </c>
       <c r="I191" t="s">
         <v>1244</v>
@@ -15227,13 +15227,13 @@
         <v>96.90000000000001</v>
       </c>
       <c r="G194">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H194">
-        <v>1.96</v>
+        <v>1.34</v>
       </c>
       <c r="I194" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J194" t="s">
         <v>1249</v>
@@ -15262,13 +15262,13 @@
         <v>16.2</v>
       </c>
       <c r="G195">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H195">
-        <v>9.880000000000001</v>
+        <v>5.93</v>
       </c>
       <c r="I195" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J195" t="s">
         <v>1249</v>
@@ -15297,10 +15297,10 @@
         <v>26.9</v>
       </c>
       <c r="G196">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="H196">
-        <v>7.43</v>
+        <v>5.95</v>
       </c>
       <c r="I196" t="s">
         <v>1244</v>
@@ -15332,10 +15332,10 @@
         <v>62</v>
       </c>
       <c r="G197">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="H197">
-        <v>3.71</v>
+        <v>3.39</v>
       </c>
       <c r="I197" t="s">
         <v>1244</v>
@@ -15367,13 +15367,13 @@
         <v>152</v>
       </c>
       <c r="G198">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H198">
-        <v>1.64</v>
+        <v>0.99</v>
       </c>
       <c r="I198" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J198" t="s">
         <v>1249</v>
@@ -15440,10 +15440,10 @@
         <v>100</v>
       </c>
       <c r="H200">
-        <v>1.69</v>
+        <v>2.42</v>
       </c>
       <c r="I200" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J200" t="s">
         <v>1252</v>
@@ -15472,13 +15472,13 @@
         <v>104</v>
       </c>
       <c r="G201">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H201">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="I201" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J201" t="s">
         <v>1249</v>
@@ -15580,10 +15580,10 @@
         <v>40</v>
       </c>
       <c r="H204">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="I204" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J204" t="s">
         <v>1252</v>
@@ -15612,13 +15612,13 @@
         <v>16</v>
       </c>
       <c r="G205">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="H205">
-        <v>13.12</v>
+        <v>16.25</v>
       </c>
       <c r="I205" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J205" t="s">
         <v>1252</v>
@@ -15682,10 +15682,10 @@
         <v>32.85</v>
       </c>
       <c r="G207">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="H207">
-        <v>8.83</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="I207" t="s">
         <v>1244</v>
@@ -15717,10 +15717,10 @@
         <v>20.2</v>
       </c>
       <c r="G208">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H208">
-        <v>17.33</v>
+        <v>12.38</v>
       </c>
       <c r="I208" t="s">
         <v>1244</v>
@@ -15752,13 +15752,13 @@
         <v>73.3</v>
       </c>
       <c r="G209">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="H209">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="I209" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J209" t="s">
         <v>1249</v>
@@ -15787,13 +15787,13 @@
         <v>10.1</v>
       </c>
       <c r="G210">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H210">
-        <v>8.91</v>
+        <v>5.35</v>
       </c>
       <c r="I210" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J210" t="s">
         <v>1249</v>
@@ -15828,7 +15828,7 @@
         <v>0.99</v>
       </c>
       <c r="I211" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K211" t="s">
         <v>1455</v>
@@ -15854,10 +15854,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="G212">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="H212">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="I212" t="s">
         <v>1244</v>
@@ -15927,10 +15927,10 @@
         <v>100</v>
       </c>
       <c r="H214">
-        <v>11.25</v>
+        <v>16.08</v>
       </c>
       <c r="I214" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J214" t="s">
         <v>1255</v>
@@ -15959,13 +15959,13 @@
         <v>207.5</v>
       </c>
       <c r="G215">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="H215">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="I215" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J215" t="s">
         <v>1252</v>
@@ -15994,10 +15994,10 @@
         <v>34.75</v>
       </c>
       <c r="G216">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="H216">
-        <v>11.51</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I216" t="s">
         <v>1244</v>
@@ -16064,7 +16064,7 @@
         <v>40</v>
       </c>
       <c r="H218">
-        <v>0.36</v>
+        <v>0.51</v>
       </c>
       <c r="I218" t="s">
         <v>1245</v>
@@ -16134,10 +16134,10 @@
         <v>135</v>
       </c>
       <c r="H220">
-        <v>3.82</v>
+        <v>5.45</v>
       </c>
       <c r="I220" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J220" t="s">
         <v>1252</v>
@@ -16172,7 +16172,7 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J221" t="s">
         <v>1249</v>
@@ -16201,13 +16201,13 @@
         <v>25.7</v>
       </c>
       <c r="G222">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H222">
-        <v>1.09</v>
+        <v>0.78</v>
       </c>
       <c r="I222" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J222" t="s">
         <v>1249</v>
@@ -16236,10 +16236,10 @@
         <v>21</v>
       </c>
       <c r="G223">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H223">
-        <v>6.19</v>
+        <v>5.24</v>
       </c>
       <c r="I223" t="s">
         <v>1244</v>
@@ -16271,10 +16271,10 @@
         <v>17.55</v>
       </c>
       <c r="G224">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H224">
-        <v>8.550000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="I224" t="s">
         <v>1244</v>
@@ -16306,13 +16306,13 @@
         <v>33.55</v>
       </c>
       <c r="G225">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H225">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="I225" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J225" t="s">
         <v>1251</v>
@@ -16341,10 +16341,10 @@
         <v>69</v>
       </c>
       <c r="G226">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="H226">
-        <v>3.62</v>
+        <v>3.04</v>
       </c>
       <c r="I226" t="s">
         <v>1244</v>
@@ -16382,7 +16382,7 @@
         <v>5.99</v>
       </c>
       <c r="I227" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J227" t="s">
         <v>1249</v>
@@ -16414,7 +16414,7 @@
         <v>40</v>
       </c>
       <c r="H228">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="I228" t="s">
         <v>1245</v>
@@ -16446,10 +16446,10 @@
         <v>16.5</v>
       </c>
       <c r="G229">
-        <v>3757</v>
+        <v>3717</v>
       </c>
       <c r="H229">
-        <v>364.32</v>
+        <v>360.44</v>
       </c>
       <c r="I229" t="s">
         <v>1244</v>
@@ -16522,7 +16522,7 @@
         <v>4.33</v>
       </c>
       <c r="I231" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J231" t="s">
         <v>1249</v>
@@ -16551,13 +16551,13 @@
         <v>16.4</v>
       </c>
       <c r="G232">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H232">
-        <v>2.44</v>
+        <v>1.46</v>
       </c>
       <c r="I232" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J232" t="s">
         <v>1249</v>
@@ -16592,7 +16592,7 @@
         <v>0.48</v>
       </c>
       <c r="I233" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K233" t="s">
         <v>1474</v>
@@ -16624,7 +16624,7 @@
         <v>0.97</v>
       </c>
       <c r="I234" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K234" t="s">
         <v>1475</v>
@@ -16650,13 +16650,13 @@
         <v>20.8</v>
       </c>
       <c r="G235">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H235">
-        <v>0.48</v>
+        <v>0.29</v>
       </c>
       <c r="I235" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K235" t="s">
         <v>1476</v>
@@ -16685,10 +16685,10 @@
         <v>55</v>
       </c>
       <c r="H236">
-        <v>0.9</v>
+        <v>1.29</v>
       </c>
       <c r="I236" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J236" t="s">
         <v>1253</v>
@@ -16723,7 +16723,7 @@
         <v>1.88</v>
       </c>
       <c r="I237" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="K237" t="s">
         <v>1478</v>
@@ -16755,7 +16755,7 @@
         <v>10.93</v>
       </c>
       <c r="I238" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J238" t="s">
         <v>1249</v>
@@ -16784,10 +16784,10 @@
         <v>33.85</v>
       </c>
       <c r="G239">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H239">
-        <v>11.82</v>
+        <v>12.41</v>
       </c>
       <c r="I239" t="s">
         <v>1244</v>
@@ -16819,10 +16819,10 @@
         <v>20.1</v>
       </c>
       <c r="G240">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="H240">
-        <v>29.85</v>
+        <v>26.27</v>
       </c>
       <c r="I240" t="s">
         <v>1244</v>
@@ -16860,7 +16860,7 @@
         <v>7.39</v>
       </c>
       <c r="I241" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J241" t="s">
         <v>1249</v>
@@ -16889,10 +16889,10 @@
         <v>24.75</v>
       </c>
       <c r="G242">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="H242">
-        <v>23.27</v>
+        <v>20.69</v>
       </c>
       <c r="I242" t="s">
         <v>1244</v>
@@ -16930,7 +16930,7 @@
         <v>9.82</v>
       </c>
       <c r="I243" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J243" t="s">
         <v>1249</v>
@@ -16959,13 +16959,13 @@
         <v>31.75</v>
       </c>
       <c r="G244">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="H244">
-        <v>11.38</v>
+        <v>15.5</v>
       </c>
       <c r="I244" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J244" t="s">
         <v>1253</v>
@@ -16994,10 +16994,10 @@
         <v>51.3</v>
       </c>
       <c r="G245">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="H245">
-        <v>9.279999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="I245" t="s">
         <v>1244</v>
@@ -17029,10 +17029,10 @@
         <v>5.26</v>
       </c>
       <c r="G246">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="H246">
-        <v>53.23</v>
+        <v>42.59</v>
       </c>
       <c r="I246" t="s">
         <v>1244</v>
@@ -17064,10 +17064,10 @@
         <v>12.25</v>
       </c>
       <c r="G247">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H247">
-        <v>8.16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I247" t="s">
         <v>1244</v>
@@ -17099,10 +17099,10 @@
         <v>7</v>
       </c>
       <c r="G248">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="H248">
-        <v>46.29</v>
+        <v>39.43</v>
       </c>
       <c r="I248" t="s">
         <v>1244</v>
@@ -17140,7 +17140,7 @@
         <v>0.1</v>
       </c>
       <c r="I249" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="K249" t="s">
         <v>1489</v>
@@ -17166,13 +17166,13 @@
         <v>78</v>
       </c>
       <c r="G250">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="H250">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="I250" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="K250" t="s">
         <v>1490</v>
@@ -17271,7 +17271,7 @@
         <v>1.84</v>
       </c>
       <c r="I253" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J253" t="s">
         <v>1249</v>
@@ -17300,13 +17300,13 @@
         <v>12.3</v>
       </c>
       <c r="G254">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="H254">
-        <v>13.37</v>
+        <v>17.48</v>
       </c>
       <c r="I254" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J254" t="s">
         <v>1252</v>
@@ -17335,10 +17335,10 @@
         <v>118.5</v>
       </c>
       <c r="G255">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="H255">
-        <v>2.73</v>
+        <v>2.33</v>
       </c>
       <c r="I255" t="s">
         <v>1244</v>
@@ -17370,10 +17370,10 @@
         <v>1865</v>
       </c>
       <c r="G256">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H256">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I256" t="s">
         <v>1248</v>
@@ -17405,10 +17405,10 @@
         <v>445</v>
       </c>
       <c r="H257">
-        <v>34.47</v>
+        <v>49.25</v>
       </c>
       <c r="I257" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J257" t="s">
         <v>1252</v>
@@ -17472,13 +17472,13 @@
         <v>246.5</v>
       </c>
       <c r="G259">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="H259">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="I259" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J259" t="s">
         <v>1249</v>
@@ -17507,10 +17507,10 @@
         <v>10.15</v>
       </c>
       <c r="G260">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H260">
-        <v>19.7</v>
+        <v>17.73</v>
       </c>
       <c r="I260" t="s">
         <v>1244</v>
@@ -17542,10 +17542,10 @@
         <v>61.8</v>
       </c>
       <c r="G261">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="H261">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="I261" t="s">
         <v>1244</v>
@@ -17577,10 +17577,10 @@
         <v>108</v>
       </c>
       <c r="G262">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H262">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="I262" t="s">
         <v>1247</v>
@@ -17612,10 +17612,10 @@
         <v>21.35</v>
       </c>
       <c r="G263">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="H263">
-        <v>8.43</v>
+        <v>7.49</v>
       </c>
       <c r="I263" t="s">
         <v>1244</v>
@@ -17653,7 +17653,7 @@
         <v>1.98</v>
       </c>
       <c r="I264" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J264" t="s">
         <v>1249</v>
@@ -17685,10 +17685,10 @@
         <v>205</v>
       </c>
       <c r="H265">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="I265" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J265" t="s">
         <v>1252</v>
@@ -17717,13 +17717,13 @@
         <v>68</v>
       </c>
       <c r="G266">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H266">
-        <v>2.35</v>
+        <v>1.41</v>
       </c>
       <c r="I266" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J266" t="s">
         <v>1249</v>
@@ -17752,10 +17752,10 @@
         <v>30.4</v>
       </c>
       <c r="G267">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="H267">
-        <v>14.8</v>
+        <v>14.14</v>
       </c>
       <c r="I267" t="s">
         <v>1244</v>
@@ -17828,7 +17828,7 @@
         <v>1.65</v>
       </c>
       <c r="I269" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J269" t="s">
         <v>1249</v>
@@ -17860,7 +17860,7 @@
         <v>250</v>
       </c>
       <c r="H270">
-        <v>0.74</v>
+        <v>1.06</v>
       </c>
       <c r="I270" t="s">
         <v>1246</v>
@@ -17892,10 +17892,10 @@
         <v>508</v>
       </c>
       <c r="G271">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="H271">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="I271" t="s">
         <v>1246</v>
@@ -17927,10 +17927,10 @@
         <v>23.1</v>
       </c>
       <c r="G272">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="H272">
-        <v>11.26</v>
+        <v>8.66</v>
       </c>
       <c r="I272" t="s">
         <v>1244</v>
@@ -18000,10 +18000,10 @@
         <v>250</v>
       </c>
       <c r="H274">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="I274" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J274" t="s">
         <v>1252</v>
@@ -18032,10 +18032,10 @@
         <v>21.35</v>
       </c>
       <c r="G275">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="H275">
-        <v>16.58</v>
+        <v>15.46</v>
       </c>
       <c r="I275" t="s">
         <v>1244</v>
@@ -18067,10 +18067,10 @@
         <v>15.9</v>
       </c>
       <c r="G276">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H276">
-        <v>15.72</v>
+        <v>9.43</v>
       </c>
       <c r="I276" t="s">
         <v>1244</v>
@@ -18137,10 +18137,10 @@
         <v>12.45</v>
       </c>
       <c r="G278">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H278">
-        <v>17.67</v>
+        <v>16.06</v>
       </c>
       <c r="I278" t="s">
         <v>1244</v>
@@ -18172,10 +18172,10 @@
         <v>12.9</v>
       </c>
       <c r="G279">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="H279">
-        <v>17.83</v>
+        <v>16.28</v>
       </c>
       <c r="I279" t="s">
         <v>1244</v>
@@ -18207,10 +18207,10 @@
         <v>21.3</v>
       </c>
       <c r="G280">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="H280">
-        <v>10.8</v>
+        <v>8.92</v>
       </c>
       <c r="I280" t="s">
         <v>1244</v>
@@ -18242,10 +18242,10 @@
         <v>11.1</v>
       </c>
       <c r="G281">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="H281">
-        <v>28.83</v>
+        <v>25.23</v>
       </c>
       <c r="I281" t="s">
         <v>1244</v>
@@ -18283,7 +18283,7 @@
         <v>10.7</v>
       </c>
       <c r="I282" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J282" t="s">
         <v>1249</v>
@@ -18312,10 +18312,10 @@
         <v>15.05</v>
       </c>
       <c r="G283">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="H283">
-        <v>19.27</v>
+        <v>17.94</v>
       </c>
       <c r="I283" t="s">
         <v>1244</v>
@@ -18347,10 +18347,10 @@
         <v>9.19</v>
       </c>
       <c r="G284">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H284">
-        <v>27.2</v>
+        <v>16.32</v>
       </c>
       <c r="I284" t="s">
         <v>1244</v>
@@ -18382,13 +18382,13 @@
         <v>37.45</v>
       </c>
       <c r="G285">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="H285">
-        <v>5.61</v>
+        <v>6.94</v>
       </c>
       <c r="I285" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J285" t="s">
         <v>1252</v>
@@ -18455,10 +18455,10 @@
         <v>100</v>
       </c>
       <c r="H287">
-        <v>3</v>
+        <v>4.28</v>
       </c>
       <c r="I287" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J287" t="s">
         <v>1252</v>
@@ -18487,10 +18487,10 @@
         <v>60.3</v>
       </c>
       <c r="G288">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H288">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
       <c r="I288" t="s">
         <v>1244</v>
@@ -18557,13 +18557,13 @@
         <v>92.40000000000001</v>
       </c>
       <c r="G290">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H290">
-        <v>2.06</v>
+        <v>1.41</v>
       </c>
       <c r="I290" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J290" t="s">
         <v>1249</v>
@@ -18598,7 +18598,7 @@
         <v>1.99</v>
       </c>
       <c r="I291" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J291" t="s">
         <v>1249</v>
@@ -18627,13 +18627,13 @@
         <v>23.2</v>
       </c>
       <c r="G292">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="H292">
-        <v>9.35</v>
+        <v>11.64</v>
       </c>
       <c r="I292" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J292" t="s">
         <v>1252</v>
@@ -18662,10 +18662,10 @@
         <v>31.5</v>
       </c>
       <c r="G293">
-        <v>450</v>
+        <v>390</v>
       </c>
       <c r="H293">
-        <v>14.29</v>
+        <v>12.38</v>
       </c>
       <c r="I293" t="s">
         <v>1244</v>
@@ -18697,7 +18697,7 @@
         <v>313</v>
       </c>
       <c r="G294">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H294">
         <v>0.02</v>
@@ -18738,7 +18738,7 @@
         <v>2</v>
       </c>
       <c r="I295" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J295" t="s">
         <v>1249</v>
@@ -18802,10 +18802,10 @@
         <v>25.6</v>
       </c>
       <c r="G297">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="H297">
-        <v>8.59</v>
+        <v>7.03</v>
       </c>
       <c r="I297" t="s">
         <v>1244</v>
@@ -18872,10 +18872,10 @@
         <v>1965</v>
       </c>
       <c r="G299">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="H299">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I299" t="s">
         <v>1248</v>
@@ -18907,13 +18907,13 @@
         <v>184</v>
       </c>
       <c r="G300">
-        <v>410</v>
+        <v>350</v>
       </c>
       <c r="H300">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="I300" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J300" t="s">
         <v>1249</v>
@@ -18942,13 +18942,13 @@
         <v>44.7</v>
       </c>
       <c r="G301">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H301">
-        <v>3.73</v>
+        <v>4.7</v>
       </c>
       <c r="I301" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J301" t="s">
         <v>1252</v>
@@ -18977,10 +18977,10 @@
         <v>46.5</v>
       </c>
       <c r="G302">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H302">
-        <v>4.73</v>
+        <v>3.01</v>
       </c>
       <c r="I302" t="s">
         <v>1244</v>
@@ -19012,7 +19012,7 @@
         <v>250</v>
       </c>
       <c r="H303">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="I303" t="s">
         <v>1245</v>
@@ -19047,10 +19047,10 @@
         <v>300</v>
       </c>
       <c r="H304">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="I304" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J304" t="s">
         <v>1252</v>
@@ -19117,10 +19117,10 @@
         <v>105</v>
       </c>
       <c r="H306">
-        <v>3.07</v>
+        <v>4.39</v>
       </c>
       <c r="I306" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J306" t="s">
         <v>1252</v>
@@ -19152,10 +19152,10 @@
         <v>100</v>
       </c>
       <c r="H307">
-        <v>1.38</v>
+        <v>1.96</v>
       </c>
       <c r="I307" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J307" t="s">
         <v>1252</v>
@@ -19187,10 +19187,10 @@
         <v>100</v>
       </c>
       <c r="H308">
-        <v>1.97</v>
+        <v>2.81</v>
       </c>
       <c r="I308" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J308" t="s">
         <v>1252</v>
@@ -19219,10 +19219,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="G309">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H309">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="I309" t="s">
         <v>1245</v>
@@ -19295,7 +19295,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I311" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J311" t="s">
         <v>1249</v>
@@ -19324,10 +19324,10 @@
         <v>101.5</v>
       </c>
       <c r="G312">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="H312">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="I312" t="s">
         <v>1244</v>
@@ -19394,10 +19394,10 @@
         <v>44.85</v>
       </c>
       <c r="G314">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H314">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="I314" t="s">
         <v>1245</v>
@@ -19429,13 +19429,13 @@
         <v>198</v>
       </c>
       <c r="G315">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="H315">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="I315" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J315" t="s">
         <v>1249</v>
@@ -19467,10 +19467,10 @@
         <v>200</v>
       </c>
       <c r="H316">
-        <v>0.86</v>
+        <v>1.23</v>
       </c>
       <c r="I316" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J316" t="s">
         <v>1252</v>
@@ -19531,13 +19531,13 @@
         <v>38.35</v>
       </c>
       <c r="G318">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H318">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="I318" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J318" t="s">
         <v>1249</v>
@@ -19566,13 +19566,13 @@
         <v>22.85</v>
       </c>
       <c r="G319">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H319">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="I319" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K319" t="s">
         <v>1299</v>
@@ -19630,10 +19630,10 @@
         <v>27.4</v>
       </c>
       <c r="G321">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H321">
-        <v>8.029999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I321" t="s">
         <v>1244</v>
@@ -19700,13 +19700,13 @@
         <v>151</v>
       </c>
       <c r="G323">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="H323">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="I323" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J323" t="s">
         <v>1252</v>
@@ -19811,7 +19811,7 @@
         <v>0.47</v>
       </c>
       <c r="I326" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K326" t="s">
         <v>1556</v>
@@ -19872,10 +19872,10 @@
         <v>45.65</v>
       </c>
       <c r="G328">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H328">
-        <v>4.82</v>
+        <v>3.07</v>
       </c>
       <c r="I328" t="s">
         <v>1244</v>
@@ -19942,13 +19942,13 @@
         <v>45.9</v>
       </c>
       <c r="G330">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="H330">
-        <v>3.49</v>
+        <v>2.44</v>
       </c>
       <c r="I330" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J330" t="s">
         <v>1249</v>
@@ -19977,13 +19977,13 @@
         <v>31.6</v>
       </c>
       <c r="G331">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="H331">
-        <v>7.34</v>
+        <v>6.33</v>
       </c>
       <c r="I331" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J331" t="s">
         <v>1249</v>
@@ -20047,13 +20047,13 @@
         <v>12.45</v>
       </c>
       <c r="G333">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="H333">
-        <v>10.6</v>
+        <v>9.32</v>
       </c>
       <c r="I333" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J333" t="s">
         <v>1249</v>
@@ -20082,10 +20082,10 @@
         <v>49.8</v>
       </c>
       <c r="G334">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="H334">
-        <v>9.4</v>
+        <v>8.43</v>
       </c>
       <c r="I334" t="s">
         <v>1244</v>
@@ -20120,10 +20120,10 @@
         <v>250</v>
       </c>
       <c r="H335">
-        <v>11.29</v>
+        <v>16.13</v>
       </c>
       <c r="I335" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J335" t="s">
         <v>1252</v>
@@ -20260,10 +20260,10 @@
         <v>220</v>
       </c>
       <c r="H339">
-        <v>11.04</v>
+        <v>15.77</v>
       </c>
       <c r="I339" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J339" t="s">
         <v>1252</v>
@@ -20333,7 +20333,7 @@
         <v>1.01</v>
       </c>
       <c r="I341" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K341" t="s">
         <v>1567</v>
@@ -20359,10 +20359,10 @@
         <v>19.7</v>
       </c>
       <c r="G342">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H342">
-        <v>12.69</v>
+        <v>7.61</v>
       </c>
       <c r="I342" t="s">
         <v>1244</v>
@@ -20394,10 +20394,10 @@
         <v>47.9</v>
       </c>
       <c r="G343">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H343">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="I343" t="s">
         <v>1244</v>
@@ -20429,10 +20429,10 @@
         <v>15.05</v>
       </c>
       <c r="G344">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H344">
-        <v>8.640000000000001</v>
+        <v>7.31</v>
       </c>
       <c r="I344" t="s">
         <v>1244</v>
@@ -20505,7 +20505,7 @@
         <v>5.41</v>
       </c>
       <c r="I346" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J346" t="s">
         <v>1249</v>
@@ -20534,10 +20534,10 @@
         <v>17.15</v>
       </c>
       <c r="G347">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H347">
-        <v>14.58</v>
+        <v>8.75</v>
       </c>
       <c r="I347" t="s">
         <v>1244</v>
@@ -20569,10 +20569,10 @@
         <v>197</v>
       </c>
       <c r="G348">
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="H348">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="I348" t="s">
         <v>1247</v>
@@ -20604,13 +20604,13 @@
         <v>40.15</v>
       </c>
       <c r="G349">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H349">
-        <v>3.99</v>
+        <v>2.39</v>
       </c>
       <c r="I349" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J349" t="s">
         <v>1249</v>
@@ -20642,10 +20642,10 @@
         <v>250</v>
       </c>
       <c r="H350">
-        <v>8.119999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="I350" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J350" t="s">
         <v>1252</v>
@@ -20712,7 +20712,7 @@
         <v>150</v>
       </c>
       <c r="H352">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="I352" t="s">
         <v>1245</v>
@@ -20776,10 +20776,10 @@
         <v>14.85</v>
       </c>
       <c r="G354">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H354">
-        <v>16.84</v>
+        <v>10.1</v>
       </c>
       <c r="I354" t="s">
         <v>1244</v>
@@ -20817,7 +20817,7 @@
         <v>0.97</v>
       </c>
       <c r="I355" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J355" t="s">
         <v>1249</v>
@@ -20846,10 +20846,10 @@
         <v>19.4</v>
       </c>
       <c r="G356">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="H356">
-        <v>11.34</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I356" t="s">
         <v>1244</v>
@@ -20881,10 +20881,10 @@
         <v>100</v>
       </c>
       <c r="H357">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="I357" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J357" t="s">
         <v>1252</v>
@@ -20913,13 +20913,13 @@
         <v>32.55</v>
       </c>
       <c r="G358">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="H358">
-        <v>4.3</v>
+        <v>4.92</v>
       </c>
       <c r="I358" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J358" t="s">
         <v>1252</v>
@@ -20948,10 +20948,10 @@
         <v>281</v>
       </c>
       <c r="G359">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H359">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="I359" t="s">
         <v>1246</v>
@@ -20986,10 +20986,10 @@
         <v>250</v>
       </c>
       <c r="H360">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="I360" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J360" t="s">
         <v>1252</v>
@@ -21053,13 +21053,13 @@
         <v>89.40000000000001</v>
       </c>
       <c r="G362">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H362">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="I362" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J362" t="s">
         <v>1249</v>
@@ -21088,13 +21088,13 @@
         <v>29.7</v>
       </c>
       <c r="G363">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H363">
-        <v>0.47</v>
+        <v>0.34</v>
       </c>
       <c r="I363" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J363" t="s">
         <v>1249</v>
@@ -21123,10 +21123,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="G364">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="H364">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="I364" t="s">
         <v>1244</v>
@@ -21158,10 +21158,10 @@
         <v>46.8</v>
       </c>
       <c r="G365">
-        <v>610</v>
+        <v>550</v>
       </c>
       <c r="H365">
-        <v>13.03</v>
+        <v>11.75</v>
       </c>
       <c r="I365" t="s">
         <v>1244</v>
@@ -21193,13 +21193,13 @@
         <v>24.55</v>
       </c>
       <c r="G366">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="H366">
-        <v>5.42</v>
+        <v>6.92</v>
       </c>
       <c r="I366" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J366" t="s">
         <v>1252</v>
@@ -21228,7 +21228,7 @@
         <v>1310</v>
       </c>
       <c r="G367">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H367">
         <v>0.02</v>
@@ -21266,10 +21266,10 @@
         <v>80</v>
       </c>
       <c r="H368">
-        <v>5.29</v>
+        <v>7.56</v>
       </c>
       <c r="I368" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J368" t="s">
         <v>1251</v>
@@ -21339,7 +21339,7 @@
         <v>6.47</v>
       </c>
       <c r="I370" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J370" t="s">
         <v>1249</v>
@@ -21403,10 +21403,10 @@
         <v>20.15</v>
       </c>
       <c r="G372">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H372">
-        <v>9.93</v>
+        <v>8.93</v>
       </c>
       <c r="I372" t="s">
         <v>1244</v>
@@ -21441,7 +21441,7 @@
         <v>7.75</v>
       </c>
       <c r="I373" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J373" t="s">
         <v>1249</v>
@@ -21473,10 +21473,10 @@
         <v>320</v>
       </c>
       <c r="H374">
-        <v>15.89</v>
+        <v>22.7</v>
       </c>
       <c r="I374" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J374" t="s">
         <v>1252</v>
@@ -21540,13 +21540,13 @@
         <v>288.5</v>
       </c>
       <c r="G376">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H376">
-        <v>0.87</v>
+        <v>0.52</v>
       </c>
       <c r="I376" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J376" t="s">
         <v>1249</v>
@@ -21575,10 +21575,10 @@
         <v>54.5</v>
       </c>
       <c r="G377">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H377">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="I377" t="s">
         <v>1244</v>
@@ -21642,13 +21642,13 @@
         <v>126</v>
       </c>
       <c r="G379">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H379">
-        <v>1.51</v>
+        <v>1.03</v>
       </c>
       <c r="I379" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J379" t="s">
         <v>1249</v>
@@ -21677,10 +21677,10 @@
         <v>43.4</v>
       </c>
       <c r="G380">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="H380">
-        <v>4.72</v>
+        <v>3.8</v>
       </c>
       <c r="I380" t="s">
         <v>1244</v>
@@ -21753,7 +21753,7 @@
         <v>1.53</v>
       </c>
       <c r="I382" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J382" t="s">
         <v>1249</v>
@@ -21782,10 +21782,10 @@
         <v>51.5</v>
       </c>
       <c r="G383">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="H383">
-        <v>5.05</v>
+        <v>3.88</v>
       </c>
       <c r="I383" t="s">
         <v>1244</v>
@@ -21893,7 +21893,7 @@
         <v>1.57</v>
       </c>
       <c r="I386" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J386" t="s">
         <v>1249</v>
@@ -22030,10 +22030,10 @@
         <v>60</v>
       </c>
       <c r="H390">
-        <v>0.83</v>
+        <v>1.18</v>
       </c>
       <c r="I390" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J390" t="s">
         <v>1253</v>
@@ -22097,10 +22097,10 @@
         <v>25.65</v>
       </c>
       <c r="G392">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="H392">
-        <v>7.41</v>
+        <v>5.85</v>
       </c>
       <c r="I392" t="s">
         <v>1244</v>
@@ -22129,10 +22129,10 @@
         <v>24</v>
       </c>
       <c r="G393">
-        <v>275</v>
+        <v>235</v>
       </c>
       <c r="H393">
-        <v>16.04</v>
+        <v>13.71</v>
       </c>
       <c r="I393" t="s">
         <v>1244</v>
@@ -22199,10 +22199,10 @@
         <v>49.6</v>
       </c>
       <c r="G395">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H395">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="I395" t="s">
         <v>1244</v>
@@ -22240,7 +22240,7 @@
         <v>4.18</v>
       </c>
       <c r="I396" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J396" t="s">
         <v>1249</v>
@@ -22339,10 +22339,10 @@
         <v>42.4</v>
       </c>
       <c r="G399">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H399">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="I399" t="s">
         <v>1245</v>
@@ -22371,10 +22371,10 @@
         <v>59.6</v>
       </c>
       <c r="G400">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="H400">
-        <v>4.03</v>
+        <v>2.68</v>
       </c>
       <c r="I400" t="s">
         <v>1244</v>
@@ -22406,10 +22406,10 @@
         <v>14.55</v>
       </c>
       <c r="G401">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H401">
-        <v>15.12</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="I401" t="s">
         <v>1244</v>
@@ -22476,13 +22476,13 @@
         <v>50.7</v>
       </c>
       <c r="G403">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H403">
-        <v>0.55</v>
+        <v>0.39</v>
       </c>
       <c r="I403" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J403" t="s">
         <v>1249</v>
@@ -22511,10 +22511,10 @@
         <v>16.95</v>
       </c>
       <c r="G404">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="H404">
-        <v>26.9</v>
+        <v>24.07</v>
       </c>
       <c r="I404" t="s">
         <v>1244</v>
@@ -22546,10 +22546,10 @@
         <v>10.1</v>
       </c>
       <c r="G405">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="H405">
-        <v>29.7</v>
+        <v>21.78</v>
       </c>
       <c r="I405" t="s">
         <v>1244</v>
@@ -22689,7 +22689,7 @@
         <v>3.44</v>
       </c>
       <c r="I409" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J409" t="s">
         <v>1249</v>
@@ -22721,10 +22721,10 @@
         <v>35</v>
       </c>
       <c r="H410">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="I410" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J410" t="s">
         <v>1253</v>
@@ -22759,7 +22759,7 @@
         <v>4.11</v>
       </c>
       <c r="I411" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J411" t="s">
         <v>1249</v>
@@ -22823,10 +22823,10 @@
         <v>67.7</v>
       </c>
       <c r="G413">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H413">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="I413" t="s">
         <v>1244</v>
@@ -22864,7 +22864,7 @@
         <v>0.98</v>
       </c>
       <c r="I414" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J414" t="s">
         <v>1249</v>
@@ -22934,7 +22934,7 @@
         <v>1.99</v>
       </c>
       <c r="I416" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J416" t="s">
         <v>1249</v>
@@ -22995,13 +22995,13 @@
         <v>82.7</v>
       </c>
       <c r="G418">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H418">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="I418" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J418" t="s">
         <v>1249</v>
@@ -23030,13 +23030,13 @@
         <v>56.3</v>
       </c>
       <c r="G419">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H419">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="I419" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J419" t="s">
         <v>1257</v>
@@ -23100,13 +23100,13 @@
         <v>6.43</v>
       </c>
       <c r="G421">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H421">
-        <v>20.68</v>
+        <v>20.22</v>
       </c>
       <c r="I421" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J421" t="s">
         <v>1252</v>
@@ -23135,13 +23135,13 @@
         <v>341.5</v>
       </c>
       <c r="G422">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="H422">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="I422" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J422" t="s">
         <v>1249</v>
@@ -23170,10 +23170,10 @@
         <v>42.75</v>
       </c>
       <c r="G423">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H423">
-        <v>4.68</v>
+        <v>4.21</v>
       </c>
       <c r="I423" t="s">
         <v>1244</v>
@@ -23205,13 +23205,13 @@
         <v>166</v>
       </c>
       <c r="G424">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="H424">
-        <v>0.82</v>
+        <v>0.53</v>
       </c>
       <c r="I424" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J424" t="s">
         <v>1249</v>
@@ -23246,7 +23246,7 @@
         <v>0.48</v>
       </c>
       <c r="I425" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J425" t="s">
         <v>1249</v>
@@ -23275,10 +23275,10 @@
         <v>19.45</v>
       </c>
       <c r="G426">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H426">
-        <v>5.66</v>
+        <v>4.63</v>
       </c>
       <c r="I426" t="s">
         <v>1244</v>
@@ -23313,7 +23313,7 @@
         <v>80</v>
       </c>
       <c r="H427">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="I427" t="s">
         <v>1246</v>
@@ -23412,13 +23412,13 @@
         <v>13.45</v>
       </c>
       <c r="G430">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="H430">
-        <v>13.12</v>
+        <v>13.38</v>
       </c>
       <c r="I430" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J430" t="s">
         <v>1252</v>
@@ -23549,10 +23549,10 @@
         <v>31.2</v>
       </c>
       <c r="G434">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="H434">
-        <v>6.09</v>
+        <v>5.45</v>
       </c>
       <c r="I434" t="s">
         <v>1244</v>
@@ -23651,13 +23651,13 @@
         <v>82.40000000000001</v>
       </c>
       <c r="G437">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H437">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="I437" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K437" t="s">
         <v>1649</v>
@@ -23753,10 +23753,10 @@
         <v>118</v>
       </c>
       <c r="G440">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H440">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="I440" t="s">
         <v>1247</v>
@@ -23794,7 +23794,7 @@
         <v>3.11</v>
       </c>
       <c r="I441" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J441" t="s">
         <v>1249</v>
@@ -23826,10 +23826,10 @@
         <v>125</v>
       </c>
       <c r="H442">
-        <v>3.02</v>
+        <v>4.32</v>
       </c>
       <c r="I442" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J442" t="s">
         <v>1252</v>
@@ -23861,7 +23861,7 @@
         <v>40</v>
       </c>
       <c r="H443">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="I443" t="s">
         <v>1245</v>
@@ -23931,10 +23931,10 @@
         <v>250</v>
       </c>
       <c r="H445">
-        <v>3.46</v>
+        <v>4.94</v>
       </c>
       <c r="I445" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J445" t="s">
         <v>1252</v>
@@ -23969,7 +23969,7 @@
         <v>246.89</v>
       </c>
       <c r="I446" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J446" t="s">
         <v>1249</v>
@@ -24103,10 +24103,10 @@
         <v>20.5</v>
       </c>
       <c r="G450">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="H450">
-        <v>10</v>
+        <v>9.02</v>
       </c>
       <c r="I450" t="s">
         <v>1244</v>
@@ -24138,10 +24138,10 @@
         <v>24.2</v>
       </c>
       <c r="G451">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="H451">
-        <v>6.61</v>
+        <v>5.79</v>
       </c>
       <c r="I451" t="s">
         <v>1244</v>
@@ -24179,7 +24179,7 @@
         <v>5.26</v>
       </c>
       <c r="I452" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J452" t="s">
         <v>1249</v>
@@ -24211,10 +24211,10 @@
         <v>80</v>
       </c>
       <c r="H453">
-        <v>2.17</v>
+        <v>3.11</v>
       </c>
       <c r="I453" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J453" t="s">
         <v>1252</v>
@@ -24246,10 +24246,10 @@
         <v>300</v>
       </c>
       <c r="H454">
-        <v>6.45</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="I454" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J454" t="s">
         <v>1252</v>
@@ -24284,7 +24284,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I455" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J455" t="s">
         <v>1249</v>
@@ -24389,7 +24389,7 @@
         <v>2.46</v>
       </c>
       <c r="I458" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="K458" t="s">
         <v>1667</v>
@@ -24453,7 +24453,7 @@
         <v>3.7</v>
       </c>
       <c r="I460" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J460" t="s">
         <v>1249</v>
@@ -24488,7 +24488,7 @@
         <v>3.79</v>
       </c>
       <c r="I461" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J461" t="s">
         <v>1249</v>
@@ -24517,10 +24517,10 @@
         <v>30.2</v>
       </c>
       <c r="G462">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H462">
-        <v>8.279999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="I462" t="s">
         <v>1244</v>
@@ -24590,7 +24590,7 @@
         <v>1.17</v>
       </c>
       <c r="I464" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K464" t="s">
         <v>1671</v>
@@ -24616,13 +24616,13 @@
         <v>31.5</v>
       </c>
       <c r="G465">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H465">
-        <v>3.33</v>
+        <v>4.13</v>
       </c>
       <c r="I465" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J465" t="s">
         <v>1252</v>
@@ -24657,7 +24657,7 @@
         <v>2.15</v>
       </c>
       <c r="I466" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J466" t="s">
         <v>1249</v>
@@ -24686,10 +24686,10 @@
         <v>48.6</v>
       </c>
       <c r="G467">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H467">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="I467" t="s">
         <v>1245</v>
@@ -24727,7 +24727,7 @@
         <v>3.08</v>
       </c>
       <c r="I468" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="K468" t="s">
         <v>1675</v>
@@ -24759,7 +24759,7 @@
         <v>0.48</v>
       </c>
       <c r="I469" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J469" t="s">
         <v>1249</v>
@@ -24794,7 +24794,7 @@
         <v>1.24</v>
       </c>
       <c r="I470" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K470" t="s">
         <v>1677</v>
@@ -24820,13 +24820,13 @@
         <v>23.1</v>
       </c>
       <c r="G471">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H471">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="I471" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J471" t="s">
         <v>1249</v>
@@ -24855,10 +24855,10 @@
         <v>61</v>
       </c>
       <c r="G472">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H472">
-        <v>5.74</v>
+        <v>4.1</v>
       </c>
       <c r="I472" t="s">
         <v>1244</v>
@@ -24890,13 +24890,13 @@
         <v>20.05</v>
       </c>
       <c r="G473">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H473">
-        <v>7.98</v>
+        <v>4.79</v>
       </c>
       <c r="I473" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="K473" t="s">
         <v>1680</v>
@@ -24957,10 +24957,10 @@
         <v>15.4</v>
       </c>
       <c r="G475">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H475">
-        <v>11.04</v>
+        <v>9.74</v>
       </c>
       <c r="I475" t="s">
         <v>1244</v>
@@ -24992,10 +24992,10 @@
         <v>14.1</v>
       </c>
       <c r="G476">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H476">
-        <v>11.35</v>
+        <v>8.51</v>
       </c>
       <c r="I476" t="s">
         <v>1244</v>
@@ -25100,10 +25100,10 @@
         <v>400</v>
       </c>
       <c r="H479">
-        <v>12.89</v>
+        <v>18.42</v>
       </c>
       <c r="I479" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J479" t="s">
         <v>1252</v>
@@ -25170,7 +25170,7 @@
         <v>1.75</v>
       </c>
       <c r="I481" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J481" t="s">
         <v>1249</v>
@@ -25237,10 +25237,10 @@
         <v>200</v>
       </c>
       <c r="H483">
-        <v>3.4</v>
+        <v>4.86</v>
       </c>
       <c r="I483" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J483" t="s">
         <v>1252</v>
@@ -25269,10 +25269,10 @@
         <v>55.1</v>
       </c>
       <c r="G484">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="H484">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="I484" t="s">
         <v>1244</v>
@@ -25345,7 +25345,7 @@
         <v>0.42</v>
       </c>
       <c r="I486" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J486" t="s">
         <v>1249</v>
@@ -25511,13 +25511,13 @@
         <v>26.15</v>
       </c>
       <c r="G491">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="H491">
-        <v>4.28</v>
+        <v>5.35</v>
       </c>
       <c r="I491" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J491" t="s">
         <v>1252</v>
@@ -25546,13 +25546,13 @@
         <v>106</v>
       </c>
       <c r="G492">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H492">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="I492" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J492" t="s">
         <v>1252</v>
@@ -25622,7 +25622,7 @@
         <v>0.46</v>
       </c>
       <c r="I494" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J494" t="s">
         <v>1249</v>
@@ -25657,7 +25657,7 @@
         <v>2.64</v>
       </c>
       <c r="I495" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J495" t="s">
         <v>1249</v>
@@ -25692,7 +25692,7 @@
         <v>2.58</v>
       </c>
       <c r="I496" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J496" t="s">
         <v>1249</v>
@@ -25721,10 +25721,10 @@
         <v>44.6</v>
       </c>
       <c r="G497">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H497">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="I497" t="s">
         <v>1244</v>
@@ -25762,7 +25762,7 @@
         <v>3.89</v>
       </c>
       <c r="I498" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="K498" t="s">
         <v>1700</v>
@@ -25861,10 +25861,10 @@
         <v>225</v>
       </c>
       <c r="H501">
-        <v>4.66</v>
+        <v>6.66</v>
       </c>
       <c r="I501" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J501" t="s">
         <v>1252</v>
@@ -25899,7 +25899,7 @@
         <v>3</v>
       </c>
       <c r="I502" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="K502" t="s">
         <v>1703</v>
@@ -25957,10 +25957,10 @@
         <v>15.5</v>
       </c>
       <c r="G504">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="H504">
-        <v>20.65</v>
+        <v>19.35</v>
       </c>
       <c r="I504" t="s">
         <v>1244</v>
@@ -25995,10 +25995,10 @@
         <v>250</v>
       </c>
       <c r="H505">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="I505" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J505" t="s">
         <v>1252</v>
@@ -26027,10 +26027,10 @@
         <v>31.2</v>
       </c>
       <c r="G506">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H506">
-        <v>6.09</v>
+        <v>4.17</v>
       </c>
       <c r="I506" t="s">
         <v>1244</v>
@@ -26138,7 +26138,7 @@
         <v>1.52</v>
       </c>
       <c r="I509" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J509" t="s">
         <v>1249</v>
@@ -26202,13 +26202,13 @@
         <v>464</v>
       </c>
       <c r="G511">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H511">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="I511" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="J511" t="s">
         <v>1252</v>
@@ -26237,13 +26237,13 @@
         <v>67.2</v>
       </c>
       <c r="G512">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H512">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="I512" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J512" t="s">
         <v>1249</v>
@@ -26272,10 +26272,10 @@
         <v>72.59999999999999</v>
       </c>
       <c r="G513">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H513">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="I513" t="s">
         <v>1244</v>
@@ -26313,7 +26313,7 @@
         <v>5.1</v>
       </c>
       <c r="I514" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="K514" t="s">
         <v>1713</v>
@@ -26374,13 +26374,13 @@
         <v>401.5</v>
       </c>
       <c r="G516">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="H516">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="I516" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J516" t="s">
         <v>1249</v>
@@ -26444,10 +26444,10 @@
         <v>22.5</v>
       </c>
       <c r="G518">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="H518">
-        <v>10.22</v>
+        <v>8.44</v>
       </c>
       <c r="I518" t="s">
         <v>1244</v>
@@ -26485,7 +26485,7 @@
         <v>2.66</v>
       </c>
       <c r="I519" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J519" t="s">
         <v>1249</v>
@@ -26549,10 +26549,10 @@
         <v>10.5</v>
       </c>
       <c r="G521">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H521">
-        <v>23.81</v>
+        <v>14.29</v>
       </c>
       <c r="I521" t="s">
         <v>1244</v>
@@ -26590,7 +26590,7 @@
         <v>0.76</v>
       </c>
       <c r="I522" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J522" t="s">
         <v>1249</v>
@@ -26654,13 +26654,13 @@
         <v>63.9</v>
       </c>
       <c r="G524">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H524">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="I524" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J524" t="s">
         <v>1249</v>
@@ -26695,7 +26695,7 @@
         <v>3.88</v>
       </c>
       <c r="I525" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J525" t="s">
         <v>1249</v>
@@ -26727,7 +26727,7 @@
         <v>150</v>
       </c>
       <c r="H526">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="I526" t="s">
         <v>1246</v>
@@ -26794,10 +26794,10 @@
         <v>16.5</v>
       </c>
       <c r="G528">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H528">
-        <v>13.33</v>
+        <v>8.48</v>
       </c>
       <c r="I528" t="s">
         <v>1244</v>
@@ -26829,10 +26829,10 @@
         <v>73</v>
       </c>
       <c r="G529">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H529">
-        <v>0.74</v>
+        <v>0.58</v>
       </c>
       <c r="I529" t="s">
         <v>1246</v>
@@ -26864,10 +26864,10 @@
         <v>31.3</v>
       </c>
       <c r="G530">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H530">
-        <v>7.99</v>
+        <v>4.79</v>
       </c>
       <c r="I530" t="s">
         <v>1244</v>
@@ -26899,13 +26899,13 @@
         <v>45.9</v>
       </c>
       <c r="G531">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H531">
-        <v>1.18</v>
+        <v>0.92</v>
       </c>
       <c r="I531" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J531" t="s">
         <v>1249</v>
@@ -26972,10 +26972,10 @@
         <v>250</v>
       </c>
       <c r="H533">
-        <v>8.01</v>
+        <v>11.44</v>
       </c>
       <c r="I533" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J533" t="s">
         <v>1252</v>
@@ -27010,7 +27010,7 @@
         <v>0.85</v>
       </c>
       <c r="I534" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J534" t="s">
         <v>1249</v>
@@ -27080,7 +27080,7 @@
         <v>0.51</v>
       </c>
       <c r="I536" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K536" t="s">
         <v>1733</v>
@@ -27106,10 +27106,10 @@
         <v>59.6</v>
       </c>
       <c r="G537">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H537">
-        <v>4.43</v>
+        <v>4.03</v>
       </c>
       <c r="I537" t="s">
         <v>1244</v>
@@ -27141,10 +27141,10 @@
         <v>73.7</v>
       </c>
       <c r="G538">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H538">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="I538" t="s">
         <v>1245</v>
@@ -27173,10 +27173,10 @@
         <v>23.15</v>
       </c>
       <c r="G539">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H539">
-        <v>15.12</v>
+        <v>10.8</v>
       </c>
       <c r="I539" t="s">
         <v>1244</v>
@@ -27211,10 +27211,10 @@
         <v>100</v>
       </c>
       <c r="H540">
-        <v>2.61</v>
+        <v>3.73</v>
       </c>
       <c r="I540" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J540" t="s">
         <v>1252</v>
@@ -27278,10 +27278,10 @@
         <v>7.58</v>
       </c>
       <c r="G542">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H542">
-        <v>29.02</v>
+        <v>18.47</v>
       </c>
       <c r="I542" t="s">
         <v>1244</v>
@@ -27348,13 +27348,13 @@
         <v>81.09999999999999</v>
       </c>
       <c r="G544">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="H544">
-        <v>2.76</v>
+        <v>1.97</v>
       </c>
       <c r="I544" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J544" t="s">
         <v>1249</v>
@@ -27383,13 +27383,13 @@
         <v>314</v>
       </c>
       <c r="G545">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H545">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="I545" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J545" t="s">
         <v>1249</v>
@@ -27418,10 +27418,10 @@
         <v>39.45</v>
       </c>
       <c r="G546">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="H546">
-        <v>9.130000000000001</v>
+        <v>5.48</v>
       </c>
       <c r="I546" t="s">
         <v>1244</v>
@@ -27459,7 +27459,7 @@
         <v>1.93</v>
       </c>
       <c r="I547" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J547" t="s">
         <v>1249</v>
@@ -27488,10 +27488,10 @@
         <v>30.95</v>
       </c>
       <c r="G548">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="H548">
-        <v>7.11</v>
+        <v>5.17</v>
       </c>
       <c r="I548" t="s">
         <v>1244</v>
@@ -27529,7 +27529,7 @@
         <v>1.5</v>
       </c>
       <c r="I549" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J549" t="s">
         <v>1249</v>
@@ -27558,13 +27558,13 @@
         <v>19.7</v>
       </c>
       <c r="G550">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H550">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="I550" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K550" t="s">
         <v>1746</v>
@@ -27590,13 +27590,13 @@
         <v>20.3</v>
       </c>
       <c r="G551">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="H551">
-        <v>12.55</v>
+        <v>13.79</v>
       </c>
       <c r="I551" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J551" t="s">
         <v>1252</v>
@@ -27701,7 +27701,7 @@
         <v>3.42</v>
       </c>
       <c r="I554" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J554" t="s">
         <v>1249</v>
@@ -27730,10 +27730,10 @@
         <v>14.55</v>
       </c>
       <c r="G555">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H555">
-        <v>8.93</v>
+        <v>7.56</v>
       </c>
       <c r="I555" t="s">
         <v>1244</v>
@@ -27800,13 +27800,13 @@
         <v>224</v>
       </c>
       <c r="G557">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H557">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="I557" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K557" t="s">
         <v>1751</v>
@@ -27832,10 +27832,10 @@
         <v>112</v>
       </c>
       <c r="G558">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="H558">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="I558" t="s">
         <v>1244</v>
@@ -27899,13 +27899,13 @@
         <v>106.5</v>
       </c>
       <c r="G560">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="H560">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="I560" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J560" t="s">
         <v>1249</v>
@@ -27934,13 +27934,13 @@
         <v>40.75</v>
       </c>
       <c r="G561">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H561">
-        <v>3.93</v>
+        <v>2.36</v>
       </c>
       <c r="I561" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J561" t="s">
         <v>1249</v>
@@ -27969,10 +27969,10 @@
         <v>9.93</v>
       </c>
       <c r="G562">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="H562">
-        <v>20.64</v>
+        <v>16.62</v>
       </c>
       <c r="I562" t="s">
         <v>1244</v>
@@ -28039,13 +28039,13 @@
         <v>62.4</v>
       </c>
       <c r="G564">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="H564">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="I564" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J564" t="s">
         <v>1249</v>
@@ -28074,10 +28074,10 @@
         <v>8.17</v>
       </c>
       <c r="G565">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="H565">
-        <v>28.76</v>
+        <v>18.97</v>
       </c>
       <c r="I565" t="s">
         <v>1244</v>
@@ -28109,10 +28109,10 @@
         <v>14.8</v>
       </c>
       <c r="G566">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H566">
-        <v>14.59</v>
+        <v>16.22</v>
       </c>
       <c r="I566" t="s">
         <v>1244</v>
@@ -28150,7 +28150,7 @@
         <v>2.27</v>
       </c>
       <c r="I567" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="K567" t="s">
         <v>1760</v>
@@ -28211,13 +28211,13 @@
         <v>17.65</v>
       </c>
       <c r="G569">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H569">
-        <v>9.07</v>
+        <v>5.44</v>
       </c>
       <c r="I569" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J569" t="s">
         <v>1249</v>
@@ -28246,10 +28246,10 @@
         <v>16.55</v>
       </c>
       <c r="G570">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="H570">
-        <v>15.59</v>
+        <v>14.14</v>
       </c>
       <c r="I570" t="s">
         <v>1244</v>
@@ -28316,10 +28316,10 @@
         <v>3.78</v>
       </c>
       <c r="G572">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="H572">
-        <v>76.19</v>
+        <v>50.79</v>
       </c>
       <c r="I572" t="s">
         <v>1244</v>
@@ -28354,10 +28354,10 @@
         <v>80</v>
       </c>
       <c r="H573">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="I573" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J573" t="s">
         <v>1252</v>
@@ -28392,7 +28392,7 @@
         <v>0.87</v>
       </c>
       <c r="I574" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K574" t="s">
         <v>1475</v>
@@ -28453,13 +28453,13 @@
         <v>27.8</v>
       </c>
       <c r="G576">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H576">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="I576" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J576" t="s">
         <v>1249</v>
@@ -28488,10 +28488,10 @@
         <v>13.3</v>
       </c>
       <c r="G577">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="H577">
-        <v>25.26</v>
+        <v>23.46</v>
       </c>
       <c r="I577" t="s">
         <v>1244</v>
@@ -28523,13 +28523,13 @@
         <v>17.25</v>
       </c>
       <c r="G578">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="H578">
-        <v>7.71</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I578" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J578" t="s">
         <v>1252</v>
@@ -28558,13 +28558,13 @@
         <v>14.45</v>
       </c>
       <c r="G579">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="H579">
-        <v>10.24</v>
+        <v>6.92</v>
       </c>
       <c r="I579" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J579" t="s">
         <v>1249</v>
@@ -28593,10 +28593,10 @@
         <v>95.09999999999999</v>
       </c>
       <c r="G580">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H580">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="I580" t="s">
         <v>1244</v>
@@ -28669,7 +28669,7 @@
         <v>3.27</v>
       </c>
       <c r="I582" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J582" t="s">
         <v>1249</v>
@@ -28698,10 +28698,10 @@
         <v>43.95</v>
       </c>
       <c r="G583">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="H583">
-        <v>12.1</v>
+        <v>11.47</v>
       </c>
       <c r="I583" t="s">
         <v>1244</v>
@@ -28774,7 +28774,7 @@
         <v>2.59</v>
       </c>
       <c r="I585" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J585" t="s">
         <v>1249</v>
@@ -28803,13 +28803,13 @@
         <v>52</v>
       </c>
       <c r="G586">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="H586">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="I586" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J586" t="s">
         <v>1252</v>
@@ -28873,10 +28873,10 @@
         <v>32.5</v>
       </c>
       <c r="G588">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="H588">
-        <v>17.85</v>
+        <v>17.23</v>
       </c>
       <c r="I588" t="s">
         <v>1244</v>
@@ -28908,10 +28908,10 @@
         <v>35.1</v>
       </c>
       <c r="G589">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="H589">
-        <v>5.84</v>
+        <v>5.27</v>
       </c>
       <c r="I589" t="s">
         <v>1244</v>
@@ -28946,10 +28946,10 @@
         <v>235</v>
       </c>
       <c r="H590">
-        <v>11.15</v>
+        <v>15.93</v>
       </c>
       <c r="I590" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J590" t="s">
         <v>1252</v>
@@ -28978,13 +28978,13 @@
         <v>31.45</v>
       </c>
       <c r="G591">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H591">
-        <v>3.92</v>
+        <v>5.09</v>
       </c>
       <c r="I591" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J591" t="s">
         <v>1252</v>
@@ -29013,10 +29013,10 @@
         <v>23.75</v>
       </c>
       <c r="G592">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H592">
-        <v>5.47</v>
+        <v>4.63</v>
       </c>
       <c r="I592" t="s">
         <v>1244</v>
@@ -29051,7 +29051,7 @@
         <v>200</v>
       </c>
       <c r="H593">
-        <v>0.49</v>
+        <v>0.71</v>
       </c>
       <c r="I593" t="s">
         <v>1246</v>
@@ -29089,7 +29089,7 @@
         <v>5.54</v>
       </c>
       <c r="I594" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J594" t="s">
         <v>1249</v>
@@ -29229,7 +29229,7 @@
         <v>1.74</v>
       </c>
       <c r="I598" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J598" t="s">
         <v>1249</v>
@@ -29258,10 +29258,10 @@
         <v>29.15</v>
       </c>
       <c r="G599">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H599">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="I599" t="s">
         <v>1245</v>
@@ -29293,13 +29293,13 @@
         <v>19.1</v>
       </c>
       <c r="G600">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="H600">
-        <v>9.24</v>
+        <v>9.42</v>
       </c>
       <c r="I600" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J600" t="s">
         <v>1252</v>
@@ -29328,10 +29328,10 @@
         <v>16.85</v>
       </c>
       <c r="G601">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="H601">
-        <v>13.06</v>
+        <v>9.5</v>
       </c>
       <c r="I601" t="s">
         <v>1244</v>
@@ -29363,13 +29363,13 @@
         <v>19.65</v>
       </c>
       <c r="G602">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H602">
-        <v>4.48</v>
+        <v>3.66</v>
       </c>
       <c r="I602" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J602" t="s">
         <v>1249</v>
@@ -29398,13 +29398,13 @@
         <v>18.8</v>
       </c>
       <c r="G603">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H603">
-        <v>8.19</v>
+        <v>10.64</v>
       </c>
       <c r="I603" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J603" t="s">
         <v>1252</v>
@@ -29433,13 +29433,13 @@
         <v>16.15</v>
       </c>
       <c r="G604">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H604">
-        <v>5.45</v>
+        <v>4.46</v>
       </c>
       <c r="I604" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J604" t="s">
         <v>1249</v>
@@ -29468,10 +29468,10 @@
         <v>41.5</v>
       </c>
       <c r="G605">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H605">
-        <v>5.3</v>
+        <v>3.37</v>
       </c>
       <c r="I605" t="s">
         <v>1244</v>
@@ -29509,7 +29509,7 @@
         <v>1.85</v>
       </c>
       <c r="I606" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J606" t="s">
         <v>1249</v>
@@ -29538,10 +29538,10 @@
         <v>12.55</v>
       </c>
       <c r="G607">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H607">
-        <v>19.92</v>
+        <v>11.95</v>
       </c>
       <c r="I607" t="s">
         <v>1244</v>
@@ -29608,10 +29608,10 @@
         <v>13.2</v>
       </c>
       <c r="G609">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="H609">
-        <v>23.64</v>
+        <v>12.73</v>
       </c>
       <c r="I609" t="s">
         <v>1244</v>
@@ -29643,10 +29643,10 @@
         <v>16.8</v>
       </c>
       <c r="G610">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="H610">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="I610" t="s">
         <v>1244</v>
@@ -29678,10 +29678,10 @@
         <v>50.7</v>
       </c>
       <c r="G611">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H611">
-        <v>2.56</v>
+        <v>2.17</v>
       </c>
       <c r="I611" t="s">
         <v>1244</v>
@@ -29713,13 +29713,13 @@
         <v>62.9</v>
       </c>
       <c r="G612">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="H612">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="I612" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J612" t="s">
         <v>1252</v>
@@ -29748,10 +29748,10 @@
         <v>26.85</v>
       </c>
       <c r="G613">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="H613">
-        <v>12.29</v>
+        <v>11.55</v>
       </c>
       <c r="I613" t="s">
         <v>1244</v>
@@ -29885,10 +29885,10 @@
         <v>14.2</v>
       </c>
       <c r="G617">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H617">
-        <v>17.61</v>
+        <v>10.56</v>
       </c>
       <c r="I617" t="s">
         <v>1244</v>
@@ -29926,7 +29926,7 @@
         <v>4.85</v>
       </c>
       <c r="I618" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J618" t="s">
         <v>1249</v>
@@ -29955,10 +29955,10 @@
         <v>684</v>
       </c>
       <c r="G619">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H619">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I619" t="s">
         <v>1248</v>
@@ -29990,13 +29990,13 @@
         <v>94</v>
       </c>
       <c r="G620">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H620">
-        <v>2.66</v>
+        <v>1.6</v>
       </c>
       <c r="I620" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J620" t="s">
         <v>1249</v>
@@ -30025,13 +30025,13 @@
         <v>44.7</v>
       </c>
       <c r="G621">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H621">
-        <v>3.91</v>
+        <v>5.15</v>
       </c>
       <c r="I621" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J621" t="s">
         <v>1252</v>
@@ -30095,13 +30095,13 @@
         <v>99.5</v>
       </c>
       <c r="G623">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="H623">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="I623" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J623" t="s">
         <v>1249</v>
@@ -30130,10 +30130,10 @@
         <v>175.5</v>
       </c>
       <c r="G624">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H624">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="I624" t="s">
         <v>1245</v>
@@ -30165,10 +30165,10 @@
         <v>150</v>
       </c>
       <c r="H625">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="I625" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J625" t="s">
         <v>1252</v>
@@ -30203,7 +30203,7 @@
         <v>0.7</v>
       </c>
       <c r="I626" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J626" t="s">
         <v>1249</v>
@@ -30232,10 +30232,10 @@
         <v>52.8</v>
       </c>
       <c r="G627">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="H627">
-        <v>6.59</v>
+        <v>6.14</v>
       </c>
       <c r="I627" t="s">
         <v>1244</v>
@@ -30267,13 +30267,13 @@
         <v>51.5</v>
       </c>
       <c r="G628">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H628">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="I628" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J628" t="s">
         <v>1252</v>
@@ -30302,13 +30302,13 @@
         <v>111</v>
       </c>
       <c r="G629">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H629">
-        <v>1.17</v>
+        <v>0.99</v>
       </c>
       <c r="I629" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J629" t="s">
         <v>1249</v>
@@ -30343,7 +30343,7 @@
         <v>1.57</v>
       </c>
       <c r="I630" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J630" t="s">
         <v>1249</v>
@@ -30378,7 +30378,7 @@
         <v>2.51</v>
       </c>
       <c r="I631" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J631" t="s">
         <v>1249</v>
@@ -30413,7 +30413,7 @@
         <v>1.51</v>
       </c>
       <c r="I632" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J632" t="s">
         <v>1249</v>
@@ -30477,13 +30477,13 @@
         <v>38.2</v>
       </c>
       <c r="G634">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="H634">
-        <v>3.25</v>
+        <v>2.41</v>
       </c>
       <c r="I634" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J634" t="s">
         <v>1249</v>
@@ -30518,7 +30518,7 @@
         <v>3.36</v>
       </c>
       <c r="I635" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="K635" t="s">
         <v>1429</v>
@@ -30579,13 +30579,13 @@
         <v>40.8</v>
       </c>
       <c r="G637">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="H637">
-        <v>4.8</v>
+        <v>6.37</v>
       </c>
       <c r="I637" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J637" t="s">
         <v>1252</v>
@@ -30614,13 +30614,13 @@
         <v>10.05</v>
       </c>
       <c r="G638">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="H638">
-        <v>13.23</v>
+        <v>12.94</v>
       </c>
       <c r="I638" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J638" t="s">
         <v>1252</v>
@@ -30649,10 +30649,10 @@
         <v>21.65</v>
       </c>
       <c r="G639">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H639">
-        <v>11.55</v>
+        <v>6.93</v>
       </c>
       <c r="I639" t="s">
         <v>1244</v>
@@ -30684,13 +30684,13 @@
         <v>213.5</v>
       </c>
       <c r="G640">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="H640">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="I640" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J640" t="s">
         <v>1249</v>
@@ -30719,10 +30719,10 @@
         <v>27.2</v>
       </c>
       <c r="G641">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="H641">
-        <v>7.54</v>
+        <v>6.07</v>
       </c>
       <c r="I641" t="s">
         <v>1244</v>
@@ -30760,7 +30760,7 @@
         <v>0.14</v>
       </c>
       <c r="I642" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="K642" t="s">
         <v>1824</v>
@@ -30786,10 +30786,10 @@
         <v>49</v>
       </c>
       <c r="G643">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="H643">
-        <v>4.69</v>
+        <v>3.47</v>
       </c>
       <c r="I643" t="s">
         <v>1244</v>
@@ -30961,10 +30961,10 @@
         <v>32.2</v>
       </c>
       <c r="G648">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H648">
-        <v>10.87</v>
+        <v>7.76</v>
       </c>
       <c r="I648" t="s">
         <v>1244</v>
@@ -30996,10 +30996,10 @@
         <v>16.7</v>
       </c>
       <c r="G649">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="H649">
-        <v>16.77</v>
+        <v>15.57</v>
       </c>
       <c r="I649" t="s">
         <v>1244</v>
@@ -31037,7 +31037,7 @@
         <v>1.79</v>
       </c>
       <c r="I650" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J650" t="s">
         <v>1249</v>
@@ -31072,7 +31072,7 @@
         <v>1.91</v>
       </c>
       <c r="I651" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J651" t="s">
         <v>1249</v>
@@ -31142,7 +31142,7 @@
         <v>11.17</v>
       </c>
       <c r="I653" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J653" t="s">
         <v>1249</v>
@@ -31174,10 +31174,10 @@
         <v>185</v>
       </c>
       <c r="H654">
-        <v>3.62</v>
+        <v>5.17</v>
       </c>
       <c r="I654" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J654" t="s">
         <v>1252</v>
@@ -31206,10 +31206,10 @@
         <v>55.1</v>
       </c>
       <c r="G655">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="H655">
-        <v>4.26</v>
+        <v>3.54</v>
       </c>
       <c r="I655" t="s">
         <v>1244</v>
@@ -31241,13 +31241,13 @@
         <v>23.5</v>
       </c>
       <c r="G656">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="H656">
-        <v>5.79</v>
+        <v>3.74</v>
       </c>
       <c r="I656" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J656" t="s">
         <v>1249</v>
@@ -31276,10 +31276,10 @@
         <v>150</v>
       </c>
       <c r="G657">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H657">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="I657" t="s">
         <v>1245</v>
@@ -31314,10 +31314,10 @@
         <v>150</v>
       </c>
       <c r="H658">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="I658" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="J658" t="s">
         <v>1252</v>
@@ -31346,13 +31346,13 @@
         <v>49.15</v>
       </c>
       <c r="G659">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="H659">
-        <v>4.07</v>
+        <v>3.09</v>
       </c>
       <c r="I659" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J659" t="s">
         <v>1249</v>
@@ -31381,13 +31381,13 @@
         <v>30.55</v>
       </c>
       <c r="G660">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H660">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="I660" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J660" t="s">
         <v>1249</v>
@@ -31416,10 +31416,10 @@
         <v>46.1</v>
       </c>
       <c r="G661">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="H661">
-        <v>6.25</v>
+        <v>4.16</v>
       </c>
       <c r="I661" t="s">
         <v>1244</v>
@@ -31486,10 +31486,10 @@
         <v>218.5</v>
       </c>
       <c r="G663">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="H663">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="I663" t="s">
         <v>1246</v>
@@ -31527,7 +31527,7 @@
         <v>2.42</v>
       </c>
       <c r="I664" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J664" t="s">
         <v>1249</v>
@@ -31591,10 +31591,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="G666">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H666">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="I666" t="s">
         <v>1246</v>
@@ -31632,7 +31632,7 @@
         <v>0.5</v>
       </c>
       <c r="I667" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J667" t="s">
         <v>1249</v>
@@ -31661,13 +31661,13 @@
         <v>142</v>
       </c>
       <c r="G668">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="H668">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="I668" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J668" t="s">
         <v>1252</v>
@@ -31728,13 +31728,13 @@
         <v>33.4</v>
       </c>
       <c r="G670">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="H670">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="I670" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J670" t="s">
         <v>1252</v>
@@ -31769,7 +31769,7 @@
         <v>1.69</v>
       </c>
       <c r="I671" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J671" t="s">
         <v>1249</v>
@@ -31798,13 +31798,13 @@
         <v>20</v>
       </c>
       <c r="G672">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="H672">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="I672" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J672" t="s">
         <v>1249</v>
@@ -31903,7 +31903,7 @@
         <v>100</v>
       </c>
       <c r="H675">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="I675" t="s">
         <v>1248</v>
@@ -31973,7 +31973,7 @@
         <v>0.82</v>
       </c>
       <c r="I677" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J677" t="s">
         <v>1249</v>
@@ -32005,10 +32005,10 @@
         <v>250</v>
       </c>
       <c r="H678">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="I678" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J678" t="s">
         <v>1252</v>
@@ -32043,7 +32043,7 @@
         <v>1.9</v>
       </c>
       <c r="I679" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J679" t="s">
         <v>1249</v>
@@ -32072,13 +32072,13 @@
         <v>39.5</v>
       </c>
       <c r="G680">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H680">
-        <v>4.05</v>
+        <v>2.43</v>
       </c>
       <c r="I680" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="K680" t="s">
         <v>1854</v>
@@ -32107,10 +32107,10 @@
         <v>300</v>
       </c>
       <c r="H681">
-        <v>2.46</v>
+        <v>3.51</v>
       </c>
       <c r="I681" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J681" t="s">
         <v>1252</v>
@@ -32180,7 +32180,7 @@
         <v>3.26</v>
       </c>
       <c r="I683" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J683" t="s">
         <v>1249</v>
@@ -32244,10 +32244,10 @@
         <v>89.3</v>
       </c>
       <c r="G685">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H685">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I685" t="s">
         <v>1248</v>
@@ -32317,7 +32317,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I687" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K687" t="s">
         <v>1860</v>
@@ -32349,7 +32349,7 @@
         <v>0.73</v>
       </c>
       <c r="I688" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J688" t="s">
         <v>1249</v>
@@ -32378,10 +32378,10 @@
         <v>531</v>
       </c>
       <c r="G689">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="H689">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="I689" t="s">
         <v>1245</v>
@@ -32413,13 +32413,13 @@
         <v>70.5</v>
       </c>
       <c r="G690">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H690">
-        <v>2.27</v>
+        <v>1.7</v>
       </c>
       <c r="I690" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J690" t="s">
         <v>1249</v>
@@ -32489,7 +32489,7 @@
         <v>3.6</v>
       </c>
       <c r="I692" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J692" t="s">
         <v>1249</v>
@@ -32556,7 +32556,7 @@
         <v>3.72</v>
       </c>
       <c r="I694" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J694" t="s">
         <v>1249</v>
@@ -32585,10 +32585,10 @@
         <v>198</v>
       </c>
       <c r="G695">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="H695">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="I695" t="s">
         <v>1247</v>
@@ -32623,10 +32623,10 @@
         <v>200</v>
       </c>
       <c r="H696">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="I696" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J696" t="s">
         <v>1253</v>
@@ -32655,13 +32655,13 @@
         <v>18.15</v>
       </c>
       <c r="G697">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H697">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="I697" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J697" t="s">
         <v>1249</v>
@@ -32766,7 +32766,7 @@
         <v>1.88</v>
       </c>
       <c r="I700" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J700" t="s">
         <v>1249</v>
@@ -32801,7 +32801,7 @@
         <v>3.23</v>
       </c>
       <c r="I701" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J701" t="s">
         <v>1249</v>
@@ -32836,7 +32836,7 @@
         <v>0.71</v>
       </c>
       <c r="I702" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K702" t="s">
         <v>1872</v>
@@ -32868,7 +32868,7 @@
         <v>0.13</v>
       </c>
       <c r="I703" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="J703" t="s">
         <v>1249</v>
@@ -32903,7 +32903,7 @@
         <v>0.99</v>
       </c>
       <c r="I704" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K704" t="s">
         <v>1874</v>
@@ -32929,10 +32929,10 @@
         <v>47.95</v>
       </c>
       <c r="G705">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H705">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="I705" t="s">
         <v>1245</v>
@@ -32970,7 +32970,7 @@
         <v>2.87</v>
       </c>
       <c r="I706" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J706" t="s">
         <v>1249</v>
@@ -33034,10 +33034,10 @@
         <v>45.85</v>
       </c>
       <c r="G708">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H708">
-        <v>4.58</v>
+        <v>4.14</v>
       </c>
       <c r="I708" t="s">
         <v>1244</v>
@@ -33072,7 +33072,7 @@
         <v>3.32</v>
       </c>
       <c r="I709" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="K709" t="s">
         <v>1878</v>
@@ -33104,7 +33104,7 @@
         <v>0.85</v>
       </c>
       <c r="I710" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J710" t="s">
         <v>1249</v>
@@ -33139,7 +33139,7 @@
         <v>1.57</v>
       </c>
       <c r="I711" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J711" t="s">
         <v>1249</v>
@@ -33171,7 +33171,7 @@
         <v>100</v>
       </c>
       <c r="H712">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="I712" t="s">
         <v>1245</v>
@@ -33206,7 +33206,7 @@
         <v>35</v>
       </c>
       <c r="H713">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I713" t="s">
         <v>1248</v>
@@ -33279,7 +33279,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I715" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J715" t="s">
         <v>1249</v>
@@ -33308,10 +33308,10 @@
         <v>168</v>
       </c>
       <c r="G716">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H716">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I716" t="s">
         <v>1248</v>
@@ -33378,13 +33378,13 @@
         <v>338</v>
       </c>
       <c r="G718">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H718">
-        <v>0.47</v>
+        <v>0.28</v>
       </c>
       <c r="I718" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J718" t="s">
         <v>1249</v>
@@ -33419,7 +33419,7 @@
         <v>0.52</v>
       </c>
       <c r="I719" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J719" t="s">
         <v>1249</v>
@@ -33451,7 +33451,7 @@
         <v>35</v>
       </c>
       <c r="H720">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="I720" t="s">
         <v>1245</v>
@@ -33553,10 +33553,10 @@
         <v>337</v>
       </c>
       <c r="G723">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H723">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I723" t="s">
         <v>1248</v>
@@ -33629,7 +33629,7 @@
         <v>40.41</v>
       </c>
       <c r="I725" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J725" t="s">
         <v>1249</v>
@@ -33658,10 +33658,10 @@
         <v>20.4</v>
       </c>
       <c r="G726">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="H726">
-        <v>11.27</v>
+        <v>9.31</v>
       </c>
       <c r="I726" t="s">
         <v>1244</v>
@@ -33693,10 +33693,10 @@
         <v>201</v>
       </c>
       <c r="G727">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="H727">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="I727" t="s">
         <v>1246</v>
@@ -33763,13 +33763,13 @@
         <v>13</v>
       </c>
       <c r="G729">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H729">
-        <v>8.619999999999999</v>
+        <v>7.38</v>
       </c>
       <c r="I729" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J729" t="s">
         <v>1252</v>
@@ -33801,10 +33801,10 @@
         <v>250</v>
       </c>
       <c r="H730">
-        <v>1.61</v>
+        <v>2.29</v>
       </c>
       <c r="I730" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J730" t="s">
         <v>1252</v>
@@ -33868,13 +33868,13 @@
         <v>34.7</v>
       </c>
       <c r="G732">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="H732">
-        <v>5.81</v>
+        <v>6.92</v>
       </c>
       <c r="I732" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J732" t="s">
         <v>1252</v>
@@ -33906,7 +33906,7 @@
         <v>130</v>
       </c>
       <c r="H733">
-        <v>0.64</v>
+        <v>0.92</v>
       </c>
       <c r="I733" t="s">
         <v>1246</v>
@@ -33938,13 +33938,13 @@
         <v>25.15</v>
       </c>
       <c r="G734">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="H734">
-        <v>6.96</v>
+        <v>6.76</v>
       </c>
       <c r="I734" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J734" t="s">
         <v>1252</v>
@@ -33973,10 +33973,10 @@
         <v>43.1</v>
       </c>
       <c r="G735">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H735">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="I735" t="s">
         <v>1244</v>
@@ -34011,10 +34011,10 @@
         <v>225</v>
       </c>
       <c r="H736">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="I736" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J736" t="s">
         <v>1252</v>
@@ -34043,13 +34043,13 @@
         <v>50.8</v>
       </c>
       <c r="G737">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="H737">
-        <v>5.37</v>
+        <v>7.28</v>
       </c>
       <c r="I737" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J737" t="s">
         <v>1250</v>
@@ -34078,13 +34078,13 @@
         <v>54</v>
       </c>
       <c r="G738">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H738">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="I738" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J738" t="s">
         <v>1249</v>
@@ -34119,7 +34119,7 @@
         <v>2.27</v>
       </c>
       <c r="I739" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J739" t="s">
         <v>1249</v>
@@ -34154,7 +34154,7 @@
         <v>0.67</v>
       </c>
       <c r="I740" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J740" t="s">
         <v>1249</v>
@@ -34183,13 +34183,13 @@
         <v>25.55</v>
       </c>
       <c r="G741">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H741">
-        <v>5.48</v>
+        <v>7.05</v>
       </c>
       <c r="I741" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J741" t="s">
         <v>1252</v>
@@ -34256,10 +34256,10 @@
         <v>220</v>
       </c>
       <c r="H743">
-        <v>1.52</v>
+        <v>2.18</v>
       </c>
       <c r="I743" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J743" t="s">
         <v>1252</v>
@@ -34323,10 +34323,10 @@
         <v>19.75</v>
       </c>
       <c r="G745">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="H745">
-        <v>11.14</v>
+        <v>8.1</v>
       </c>
       <c r="I745" t="s">
         <v>1244</v>
@@ -34358,13 +34358,13 @@
         <v>15.15</v>
       </c>
       <c r="G746">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H746">
-        <v>3.7</v>
+        <v>3.17</v>
       </c>
       <c r="I746" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="K746" t="s">
         <v>1907</v>
@@ -34425,13 +34425,13 @@
         <v>16.7</v>
       </c>
       <c r="G748">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H748">
-        <v>9.58</v>
+        <v>5.75</v>
       </c>
       <c r="I748" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J748" t="s">
         <v>1249</v>
@@ -34466,7 +34466,7 @@
         <v>0.87</v>
       </c>
       <c r="I749" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J749" t="s">
         <v>1249</v>
@@ -34536,7 +34536,7 @@
         <v>0.52</v>
       </c>
       <c r="I751" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J751" t="s">
         <v>1249</v>
@@ -34565,13 +34565,13 @@
         <v>17.55</v>
       </c>
       <c r="G752">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H752">
-        <v>1.82</v>
+        <v>1.37</v>
       </c>
       <c r="I752" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J752" t="s">
         <v>1249</v>
@@ -34606,7 +34606,7 @@
         <v>1.83</v>
       </c>
       <c r="I753" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J753" t="s">
         <v>1249</v>
@@ -34635,10 +34635,10 @@
         <v>32.45</v>
       </c>
       <c r="G754">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H754">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="I754" t="s">
         <v>1245</v>
@@ -34705,10 +34705,10 @@
         <v>23.85</v>
       </c>
       <c r="G756">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H756">
-        <v>10.48</v>
+        <v>6.29</v>
       </c>
       <c r="I756" t="s">
         <v>1244</v>
@@ -34778,7 +34778,7 @@
         <v>1.2</v>
       </c>
       <c r="I758" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J758" t="s">
         <v>1249</v>
@@ -34877,10 +34877,10 @@
         <v>200</v>
       </c>
       <c r="H761">
-        <v>0.9399999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="I761" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J761" t="s">
         <v>1252</v>
@@ -34912,10 +34912,10 @@
         <v>105</v>
       </c>
       <c r="H762">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="I762" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J762" t="s">
         <v>1252</v>
@@ -34944,13 +34944,13 @@
         <v>85.40000000000001</v>
       </c>
       <c r="G763">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H763">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="I763" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J763" t="s">
         <v>1252</v>
@@ -34979,13 +34979,13 @@
         <v>34.7</v>
       </c>
       <c r="G764">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H764">
-        <v>4.84</v>
+        <v>4.38</v>
       </c>
       <c r="I764" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J764" t="s">
         <v>1249</v>
@@ -35020,7 +35020,7 @@
         <v>2.04</v>
       </c>
       <c r="I765" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J765" t="s">
         <v>1249</v>
@@ -35049,10 +35049,10 @@
         <v>67</v>
       </c>
       <c r="G766">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="H766">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="I766" t="s">
         <v>1244</v>
@@ -35084,13 +35084,13 @@
         <v>87</v>
       </c>
       <c r="G767">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="H767">
-        <v>2.41</v>
+        <v>1.72</v>
       </c>
       <c r="I767" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J767" t="s">
         <v>1249</v>
@@ -35125,7 +35125,7 @@
         <v>0.66</v>
       </c>
       <c r="I768" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K768" t="s">
         <v>1925</v>
@@ -35186,10 +35186,10 @@
         <v>28.4</v>
       </c>
       <c r="G770">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="H770">
-        <v>13.94</v>
+        <v>12.25</v>
       </c>
       <c r="I770" t="s">
         <v>1244</v>
@@ -35256,10 +35256,10 @@
         <v>10.85</v>
       </c>
       <c r="G772">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="H772">
-        <v>18.89</v>
+        <v>15.21</v>
       </c>
       <c r="I772" t="s">
         <v>1244</v>
@@ -35288,10 +35288,10 @@
         <v>36.4</v>
       </c>
       <c r="G773">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="H773">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="I773" t="s">
         <v>1244</v>
@@ -35393,10 +35393,10 @@
         <v>37.7</v>
       </c>
       <c r="G776">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H776">
-        <v>6.63</v>
+        <v>3.98</v>
       </c>
       <c r="I776" t="s">
         <v>1244</v>
@@ -35469,7 +35469,7 @@
         <v>0.61</v>
       </c>
       <c r="I778" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J778" t="s">
         <v>1249</v>
@@ -35498,13 +35498,13 @@
         <v>50.9</v>
       </c>
       <c r="G779">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="H779">
-        <v>6.16</v>
+        <v>7.7</v>
       </c>
       <c r="I779" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J779" t="s">
         <v>1252</v>
@@ -35565,13 +35565,13 @@
         <v>111</v>
       </c>
       <c r="G781">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H781">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="I781" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J781" t="s">
         <v>1249</v>
@@ -35603,7 +35603,7 @@
         <v>130</v>
       </c>
       <c r="H782">
-        <v>0.52</v>
+        <v>0.75</v>
       </c>
       <c r="I782" t="s">
         <v>1246</v>
@@ -35638,10 +35638,10 @@
         <v>235</v>
       </c>
       <c r="H783">
-        <v>19.82</v>
+        <v>28.31</v>
       </c>
       <c r="I783" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J783" t="s">
         <v>1252</v>
@@ -35670,13 +35670,13 @@
         <v>34.55</v>
       </c>
       <c r="G784">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="H784">
-        <v>3.7</v>
+        <v>2.78</v>
       </c>
       <c r="I784" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J784" t="s">
         <v>1249</v>
@@ -35705,10 +35705,10 @@
         <v>1800</v>
       </c>
       <c r="G785">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="H785">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I785" t="s">
         <v>1245</v>
@@ -35845,13 +35845,13 @@
         <v>22.55</v>
       </c>
       <c r="G789">
-        <v>1090</v>
+        <v>1070</v>
       </c>
       <c r="H789">
-        <v>38.67</v>
+        <v>37.96</v>
       </c>
       <c r="I789" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="J789" t="s">
         <v>1249</v>
@@ -35880,13 +35880,13 @@
         <v>20.2</v>
       </c>
       <c r="G790">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H790">
-        <v>2.67</v>
+        <v>2.08</v>
       </c>
       <c r="I790" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J790" t="s">
         <v>1249</v>
@@ -35915,13 +35915,13 @@
         <v>7.06</v>
       </c>
       <c r="G791">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H791">
-        <v>15.86</v>
+        <v>13.6</v>
       </c>
       <c r="I791" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J791" t="s">
         <v>1252</v>
@@ -35950,10 +35950,10 @@
         <v>68</v>
       </c>
       <c r="G792">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="H792">
-        <v>4.41</v>
+        <v>4.12</v>
       </c>
       <c r="I792" t="s">
         <v>1244</v>
@@ -35991,7 +35991,7 @@
         <v>0.85</v>
       </c>
       <c r="I793" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J793" t="s">
         <v>1249</v>
@@ -36026,7 +36026,7 @@
         <v>0.82</v>
       </c>
       <c r="I794" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J794" t="s">
         <v>1249</v>
@@ -36061,7 +36061,7 @@
         <v>2.95</v>
       </c>
       <c r="I795" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J795" t="s">
         <v>1249</v>
@@ -36096,7 +36096,7 @@
         <v>6.13</v>
       </c>
       <c r="I796" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J796" t="s">
         <v>1249</v>
@@ -36166,7 +36166,7 @@
         <v>2.22</v>
       </c>
       <c r="I798" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="K798" t="s">
         <v>1948</v>
@@ -36192,10 +36192,10 @@
         <v>26.25</v>
       </c>
       <c r="G799">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="H799">
-        <v>9.6</v>
+        <v>7.77</v>
       </c>
       <c r="I799" t="s">
         <v>1244</v>
@@ -36227,13 +36227,13 @@
         <v>38.9</v>
       </c>
       <c r="G800">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H800">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="I800" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J800" t="s">
         <v>1249</v>
@@ -36265,10 +36265,10 @@
         <v>205</v>
       </c>
       <c r="H801">
-        <v>3.05</v>
+        <v>4.36</v>
       </c>
       <c r="I801" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J801" t="s">
         <v>1252</v>
@@ -36300,10 +36300,10 @@
         <v>50</v>
       </c>
       <c r="H802">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="I802" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="J802" t="s">
         <v>1252</v>
@@ -36332,13 +36332,13 @@
         <v>6.73</v>
       </c>
       <c r="G803">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H803">
-        <v>5.94</v>
+        <v>3.57</v>
       </c>
       <c r="I803" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J803" t="s">
         <v>1249</v>
@@ -36472,10 +36472,10 @@
         <v>14.8</v>
       </c>
       <c r="G807">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H807">
-        <v>16.89</v>
+        <v>10.14</v>
       </c>
       <c r="I807" t="s">
         <v>1244</v>
@@ -36609,10 +36609,10 @@
         <v>47.75</v>
       </c>
       <c r="G811">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H811">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="I811" t="s">
         <v>1245</v>
@@ -36714,10 +36714,10 @@
         <v>56.9</v>
       </c>
       <c r="G814">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H814">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I814" t="s">
         <v>1245</v>
@@ -36752,7 +36752,7 @@
         <v>1.11</v>
       </c>
       <c r="I815" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K815" t="s">
         <v>1963</v>
@@ -36781,10 +36781,10 @@
         <v>35</v>
       </c>
       <c r="H816">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="I816" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="J816" t="s">
         <v>1253</v>
@@ -36813,13 +36813,13 @@
         <v>127.5</v>
       </c>
       <c r="G817">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H817">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="I817" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="J817" t="s">
         <v>1249</v>
@@ -36854,7 +36854,7 @@
         <v>2.51</v>
       </c>
       <c r="I818" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J818" t="s">
         <v>1249</v>
